--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CE13101-63F3-498B-B4CD-AEE50040FFEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE556B1-9AFD-4D2B-9966-7A3BB9978EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3235" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="601">
   <si>
     <t>제조사</t>
   </si>
@@ -2000,7 +2000,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HyundaiDBTable" displayName="HyundaiDBTable" ref="A1:H184">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="HyundaiDBTable" displayName="HyundaiDBTable" ref="A1:H155">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="제조사"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="차량명"/>
@@ -2182,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2450,16 +2450,16 @@
         <v>38</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
@@ -2477,13 +2477,13 @@
         <v>43</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
@@ -2495,19 +2495,17 @@
         <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>43</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
@@ -2526,10 +2524,10 @@
         <v>23</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
@@ -2545,13 +2543,13 @@
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
@@ -2563,17 +2561,19 @@
         <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="3"/>
+        <v>52</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="D16" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
@@ -2591,13 +2591,13 @@
         <v>53</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
@@ -2612,16 +2612,16 @@
         <v>52</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
@@ -2639,13 +2639,13 @@
         <v>55</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>56</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
@@ -2660,16 +2660,16 @@
         <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
@@ -2687,13 +2687,13 @@
         <v>59</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>60</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
@@ -2708,16 +2708,16 @@
         <v>52</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
@@ -2735,13 +2735,13 @@
         <v>61</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
@@ -2756,16 +2756,16 @@
         <v>52</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
@@ -2783,15 +2783,17 @@
         <v>66</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
         <v>600</v>
       </c>
@@ -2804,20 +2806,18 @@
         <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
         <v>600</v>
       </c>
@@ -2833,15 +2833,17 @@
         <v>68</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
         <v>600</v>
       </c>
@@ -2851,23 +2853,21 @@
         <v>8</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>63</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
         <v>600</v>
       </c>
@@ -2883,13 +2883,13 @@
         <v>74</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
@@ -2901,21 +2901,23 @@
         <v>8</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G30" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>578</v>
+      </c>
       <c r="H30" s="3" t="s">
         <v>600</v>
       </c>
@@ -2925,23 +2927,21 @@
         <v>8</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>578</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
         <v>600</v>
       </c>
@@ -2953,15 +2953,17 @@
       <c r="B32" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="D32" s="3" t="s">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>88</v>
+        <v>579</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
@@ -2973,19 +2975,19 @@
         <v>8</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
@@ -2997,19 +2999,19 @@
         <v>8</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3" t="s">
@@ -3021,21 +3023,23 @@
         <v>8</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G35" s="3"/>
+        <v>581</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="H35" s="3" t="s">
         <v>600</v>
       </c>
@@ -3045,19 +3049,19 @@
         <v>8</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>579</v>
+        <v>24</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
@@ -3072,16 +3076,16 @@
         <v>98</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
@@ -3096,18 +3100,20 @@
         <v>98</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="3"/>
+        <v>581</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="H38" s="3" t="s">
         <v>600</v>
       </c>
@@ -3120,20 +3126,18 @@
         <v>98</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>580</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="G39" s="3"/>
       <c r="H39" s="3" t="s">
         <v>600</v>
       </c>
@@ -3146,18 +3150,20 @@
         <v>98</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="3"/>
+        <v>581</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>580</v>
+      </c>
       <c r="H40" s="3" t="s">
         <v>600</v>
       </c>
@@ -3170,16 +3176,16 @@
         <v>98</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
@@ -3194,20 +3200,18 @@
         <v>98</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>580</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
         <v>600</v>
       </c>
@@ -3217,19 +3221,19 @@
         <v>8</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>106</v>
+        <v>46</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
@@ -3241,23 +3245,21 @@
         <v>8</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>580</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G44" s="3"/>
       <c r="H44" s="3" t="s">
         <v>600</v>
       </c>
@@ -3267,19 +3269,19 @@
         <v>8</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
@@ -3291,16 +3293,16 @@
         <v>8</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>24</v>
@@ -3318,13 +3320,13 @@
         <v>115</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>46</v>
@@ -3342,16 +3344,16 @@
         <v>115</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
@@ -3363,16 +3365,16 @@
         <v>8</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>46</v>
@@ -3387,19 +3389,19 @@
         <v>8</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G50" s="3"/>
       <c r="H50" s="3" t="s">
@@ -3411,16 +3413,16 @@
         <v>8</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>46</v>
@@ -3435,19 +3437,19 @@
         <v>8</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3" t="s">
@@ -3459,17 +3461,19 @@
         <v>8</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>137</v>
+      </c>
       <c r="D53" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3" t="s">
@@ -3481,17 +3485,19 @@
         <v>8</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C54" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="D54" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3" t="s">
@@ -3506,13 +3512,13 @@
         <v>123</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>46</v>
@@ -3530,16 +3536,16 @@
         <v>123</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3" t="s">
@@ -3554,16 +3560,16 @@
         <v>123</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3" t="s">
@@ -3578,16 +3584,16 @@
         <v>123</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3" t="s">
@@ -3602,18 +3608,20 @@
         <v>123</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G59" s="3"/>
+        <v>583</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>582</v>
+      </c>
       <c r="H59" s="3" t="s">
         <v>600</v>
       </c>
@@ -3626,16 +3634,16 @@
         <v>123</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3" t="s">
@@ -3650,16 +3658,16 @@
         <v>123</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3" t="s">
@@ -3674,18 +3682,20 @@
         <v>123</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>87</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G62" s="3"/>
+        <v>583</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>582</v>
+      </c>
       <c r="H62" s="3" t="s">
         <v>600</v>
       </c>
@@ -3698,16 +3708,16 @@
         <v>123</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3" t="s">
@@ -3719,19 +3729,19 @@
         <v>8</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3" t="s">
@@ -3743,19 +3753,19 @@
         <v>8</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3" t="s">
@@ -3767,23 +3777,21 @@
         <v>8</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>582</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
         <v>600</v>
       </c>
@@ -3793,19 +3801,19 @@
         <v>8</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
@@ -3817,21 +3825,23 @@
         <v>8</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G68" s="3"/>
+        <v>584</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H68" s="3" t="s">
         <v>600</v>
       </c>
@@ -3841,23 +3851,21 @@
         <v>8</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>582</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
         <v>600</v>
       </c>
@@ -3867,19 +3875,19 @@
         <v>8</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="3" t="s">
@@ -3891,19 +3899,19 @@
         <v>8</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="3" t="s">
@@ -3915,16 +3923,16 @@
         <v>8</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>46</v>
@@ -3939,19 +3947,19 @@
         <v>8</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="G73" s="3"/>
       <c r="H73" s="3" t="s">
@@ -3963,19 +3971,19 @@
         <v>8</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G74" s="3"/>
       <c r="H74" s="3" t="s">
@@ -3987,23 +3995,21 @@
         <v>8</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>585</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G75" s="3"/>
       <c r="H75" s="3" t="s">
         <v>600</v>
       </c>
@@ -4013,19 +4019,19 @@
         <v>8</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="G76" s="3"/>
       <c r="H76" s="3" t="s">
@@ -4037,19 +4043,19 @@
         <v>8</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="3" t="s">
@@ -4061,19 +4067,19 @@
         <v>8</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="3" t="s">
@@ -4085,19 +4091,19 @@
         <v>8</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>39</v>
+        <v>173</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="3" t="s">
@@ -4109,19 +4115,19 @@
         <v>8</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="3" t="s">
@@ -4133,21 +4139,23 @@
         <v>8</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G81" s="3"/>
+        <v>587</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>586</v>
+      </c>
       <c r="H81" s="3" t="s">
         <v>600</v>
       </c>
@@ -4157,19 +4165,19 @@
         <v>8</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="G82" s="3"/>
       <c r="H82" s="3" t="s">
@@ -4181,21 +4189,23 @@
         <v>8</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G83" s="3"/>
+        <v>588</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>586</v>
+      </c>
       <c r="H83" s="3" t="s">
         <v>600</v>
       </c>
@@ -4205,19 +4215,19 @@
         <v>8</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="3" t="s">
@@ -4229,19 +4239,19 @@
         <v>8</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="3" t="s">
@@ -4253,19 +4263,19 @@
         <v>8</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="3" t="s">
@@ -4277,19 +4287,19 @@
         <v>8</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G87" s="3"/>
       <c r="H87" s="3" t="s">
@@ -4301,19 +4311,19 @@
         <v>8</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="G88" s="3"/>
       <c r="H88" s="3" t="s">
@@ -4325,19 +4335,19 @@
         <v>8</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="G89" s="3"/>
       <c r="H89" s="3" t="s">
@@ -4349,23 +4359,21 @@
         <v>8</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>586</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G90" s="3"/>
       <c r="H90" s="3" t="s">
         <v>600</v>
       </c>
@@ -4375,19 +4383,19 @@
         <v>8</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="G91" s="3"/>
       <c r="H91" s="3" t="s">
@@ -4399,23 +4407,21 @@
         <v>8</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>586</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G92" s="3"/>
       <c r="H92" s="3" t="s">
         <v>600</v>
       </c>
@@ -4425,21 +4431,23 @@
         <v>8</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G93" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="H93" s="3" t="s">
         <v>600</v>
       </c>
@@ -4449,23 +4457,21 @@
         <v>8</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>586</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G94" s="3"/>
       <c r="H94" s="3" t="s">
         <v>600</v>
       </c>
@@ -4475,21 +4481,23 @@
         <v>8</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G95" s="3"/>
+        <v>63</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="H95" s="3" t="s">
         <v>600</v>
       </c>
@@ -4499,19 +4507,19 @@
         <v>8</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
@@ -4523,16 +4531,16 @@
         <v>8</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>46</v>
@@ -4547,19 +4555,19 @@
         <v>8</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="G98" s="3"/>
       <c r="H98" s="3" t="s">
@@ -4571,16 +4579,16 @@
         <v>8</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>54</v>
@@ -4595,19 +4603,19 @@
         <v>8</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="G100" s="3"/>
       <c r="H100" s="3" t="s">
@@ -4619,19 +4627,19 @@
         <v>8</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>194</v>
+        <v>220</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
@@ -4643,16 +4651,16 @@
         <v>8</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>63</v>
@@ -4667,19 +4675,19 @@
         <v>8</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>197</v>
+        <v>223</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>155</v>
+        <v>63</v>
       </c>
       <c r="G103" s="3"/>
       <c r="H103" s="3" t="s">
@@ -4691,19 +4699,19 @@
         <v>8</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>155</v>
+        <v>63</v>
       </c>
       <c r="G104" s="3"/>
       <c r="H104" s="3" t="s">
@@ -4715,16 +4723,16 @@
         <v>8</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>63</v>
@@ -4739,19 +4747,19 @@
         <v>8</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>201</v>
+        <v>227</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="G106" s="3"/>
       <c r="H106" s="3" t="s">
@@ -4763,22 +4771,22 @@
         <v>8</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>63</v>
+        <v>591</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>155</v>
+        <v>590</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>600</v>
@@ -4789,19 +4797,19 @@
         <v>8</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="G108" s="3"/>
       <c r="H108" s="3" t="s">
@@ -4813,23 +4821,21 @@
         <v>8</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>155</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G109" s="3"/>
       <c r="H109" s="3" t="s">
         <v>600</v>
       </c>
@@ -4842,16 +4848,16 @@
         <v>204</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>205</v>
+        <v>231</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="G110" s="3"/>
       <c r="H110" s="3" t="s">
@@ -4866,20 +4872,18 @@
         <v>204</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>579</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="G111" s="3"/>
       <c r="H111" s="3" t="s">
         <v>600</v>
       </c>
@@ -4892,20 +4896,18 @@
         <v>204</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>579</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="G112" s="3"/>
       <c r="H112" s="3" t="s">
         <v>600</v>
       </c>
@@ -4918,13 +4920,13 @@
         <v>204</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>46</v>
@@ -4942,16 +4944,16 @@
         <v>204</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="G114" s="3"/>
       <c r="H114" s="3" t="s">
@@ -4966,16 +4968,16 @@
         <v>204</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G115" s="3"/>
       <c r="H115" s="3" t="s">
@@ -4990,16 +4992,16 @@
         <v>204</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="G116" s="3"/>
       <c r="H116" s="3" t="s">
@@ -5014,16 +5016,16 @@
         <v>204</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>103</v>
+        <v>42</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="G117" s="3"/>
       <c r="H117" s="3" t="s">
@@ -5035,19 +5037,19 @@
         <v>8</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>54</v>
+        <v>592</v>
       </c>
       <c r="G118" s="3"/>
       <c r="H118" s="3" t="s">
@@ -5059,21 +5061,23 @@
         <v>8</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>218</v>
+        <v>256</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G119" s="3"/>
+        <v>589</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>593</v>
+      </c>
       <c r="H119" s="3" t="s">
         <v>600</v>
       </c>
@@ -5083,21 +5087,23 @@
         <v>8</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>75</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G120" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>596</v>
+      </c>
       <c r="H120" s="3" t="s">
         <v>600</v>
       </c>
@@ -5107,19 +5113,19 @@
         <v>8</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>97</v>
+        <v>260</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="G121" s="3"/>
       <c r="H121" s="3" t="s">
@@ -5131,19 +5137,19 @@
         <v>8</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="G122" s="3"/>
       <c r="H122" s="3" t="s">
@@ -5155,19 +5161,19 @@
         <v>8</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>224</v>
+        <v>263</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>63</v>
+        <v>596</v>
       </c>
       <c r="G123" s="3"/>
       <c r="H123" s="3" t="s">
@@ -5179,21 +5185,23 @@
         <v>8</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>226</v>
+        <v>265</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G124" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>596</v>
+      </c>
       <c r="H124" s="3" t="s">
         <v>600</v>
       </c>
@@ -5203,19 +5211,19 @@
         <v>8</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>227</v>
+        <v>265</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="G125" s="3"/>
       <c r="H125" s="3" t="s">
@@ -5227,22 +5235,22 @@
         <v>8</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>591</v>
+        <v>13</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>600</v>
@@ -5253,19 +5261,19 @@
         <v>8</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>227</v>
+        <v>267</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="G127" s="3"/>
       <c r="H127" s="3" t="s">
@@ -5277,21 +5285,23 @@
         <v>8</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G128" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>596</v>
+      </c>
       <c r="H128" s="3" t="s">
         <v>600</v>
       </c>
@@ -5301,16 +5311,16 @@
         <v>8</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>231</v>
+        <v>268</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>24</v>
@@ -5325,21 +5335,23 @@
         <v>8</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>234</v>
+        <v>271</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G130" s="3"/>
+        <v>595</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>594</v>
+      </c>
       <c r="H130" s="3" t="s">
         <v>600</v>
       </c>
@@ -5349,21 +5361,23 @@
         <v>8</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G131" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>596</v>
+      </c>
       <c r="H131" s="3" t="s">
         <v>600</v>
       </c>
@@ -5373,16 +5387,16 @@
         <v>8</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>204</v>
+        <v>273</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>236</v>
+        <v>274</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>46</v>
@@ -5397,19 +5411,19 @@
         <v>8</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>237</v>
+        <v>276</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>142</v>
+        <v>279</v>
       </c>
       <c r="G133" s="3"/>
       <c r="H133" s="3" t="s">
@@ -5421,19 +5435,19 @@
         <v>8</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>204</v>
+        <v>299</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>240</v>
+        <v>299</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="G134" s="3"/>
       <c r="H134" s="3" t="s">
@@ -5445,21 +5459,23 @@
         <v>8</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>240</v>
+        <v>310</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G135" s="3"/>
+        <v>584</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>585</v>
+      </c>
       <c r="H135" s="3" t="s">
         <v>600</v>
       </c>
@@ -5469,19 +5485,19 @@
         <v>8</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>204</v>
+        <v>305</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>240</v>
+        <v>311</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="G136" s="3"/>
       <c r="H136" s="3" t="s">
@@ -5493,21 +5509,23 @@
         <v>8</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>242</v>
+        <v>170</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="G137" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="H137" s="3" t="s">
         <v>600</v>
       </c>
@@ -5517,22 +5535,22 @@
         <v>8</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>246</v>
+        <v>312</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>589</v>
+        <v>106</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>593</v>
+        <v>24</v>
       </c>
       <c r="H138" s="3" t="s">
         <v>600</v>
@@ -5543,19 +5561,19 @@
         <v>8</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>248</v>
+        <v>315</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>40</v>
+        <v>304</v>
       </c>
       <c r="G139" s="3"/>
       <c r="H139" s="3" t="s">
@@ -5567,23 +5585,21 @@
         <v>8</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>593</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="G140" s="3"/>
       <c r="H140" s="3" t="s">
         <v>600</v>
       </c>
@@ -5593,16 +5609,16 @@
         <v>8</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>251</v>
+        <v>96</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>250</v>
+        <v>318</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>46</v>
@@ -5617,23 +5633,21 @@
         <v>8</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G142" s="3" t="s">
-        <v>593</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G142" s="3"/>
       <c r="H142" s="3" t="s">
         <v>600</v>
       </c>
@@ -5643,19 +5657,19 @@
         <v>8</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>254</v>
+        <v>322</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G143" s="3"/>
       <c r="H143" s="3" t="s">
@@ -5667,21 +5681,23 @@
         <v>8</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>71</v>
+        <v>324</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>255</v>
+        <v>325</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" s="3"/>
+        <v>599</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>578</v>
+      </c>
       <c r="H144" s="3" t="s">
         <v>600</v>
       </c>
@@ -5691,23 +5707,21 @@
         <v>8</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>256</v>
+        <v>324</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>257</v>
+        <v>23</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>245</v>
+        <v>325</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G145" s="3" t="s">
-        <v>593</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="G145" s="3"/>
       <c r="H145" s="3" t="s">
         <v>600</v>
       </c>
@@ -5717,22 +5731,22 @@
         <v>8</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>258</v>
+        <v>25</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>259</v>
+        <v>327</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>13</v>
+        <v>599</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="H146" s="3" t="s">
         <v>600</v>
@@ -5743,19 +5757,19 @@
         <v>8</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>260</v>
+        <v>25</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>24</v>
+        <v>155</v>
       </c>
       <c r="G147" s="3"/>
       <c r="H147" s="3" t="s">
@@ -5767,19 +5781,19 @@
         <v>8</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>258</v>
+        <v>328</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>259</v>
+        <v>329</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>24</v>
+        <v>321</v>
       </c>
       <c r="G148" s="3"/>
       <c r="H148" s="3" t="s">
@@ -5791,19 +5805,19 @@
         <v>8</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G149" s="3"/>
       <c r="H149" s="3" t="s">
@@ -5815,23 +5829,21 @@
         <v>8</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G150" s="3" t="s">
-        <v>596</v>
-      </c>
+        <v>592</v>
+      </c>
+      <c r="G150" s="3"/>
       <c r="H150" s="3" t="s">
         <v>600</v>
       </c>
@@ -5841,19 +5853,19 @@
         <v>8</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>265</v>
+        <v>335</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>24</v>
+        <v>321</v>
       </c>
       <c r="G151" s="3"/>
       <c r="H151" s="3" t="s">
@@ -5865,23 +5877,21 @@
         <v>8</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G152" s="3" t="s">
-        <v>596</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="G152" s="3"/>
       <c r="H152" s="3" t="s">
         <v>600</v>
       </c>
@@ -5891,19 +5901,19 @@
         <v>8</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>266</v>
+        <v>338</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>267</v>
+        <v>339</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>24</v>
+        <v>597</v>
       </c>
       <c r="G153" s="3"/>
       <c r="H153" s="3" t="s">
@@ -5915,23 +5925,21 @@
         <v>8</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>268</v>
+        <v>338</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G154" s="3" t="s">
-        <v>596</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="G154" s="3"/>
       <c r="H154" s="3" t="s">
         <v>600</v>
       </c>
@@ -5941,738 +5949,28 @@
         <v>8</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>245</v>
+        <v>313</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>269</v>
+        <v>341</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>24</v>
+        <v>598</v>
       </c>
       <c r="G155" s="3"/>
       <c r="H155" s="3" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C156" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D156" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F156" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="G156" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="H156" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B157" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C157" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="D157" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E157" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F157" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G157" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="H157" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B158" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="C158" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="D158" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E158" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F158" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G158" s="3"/>
-      <c r="H158" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
-      <c r="A159" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D159" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E159" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F159" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="G159" s="3"/>
-      <c r="H159" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B160" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="D160" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E160" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="F160" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="G160" s="3"/>
-      <c r="H160" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="A161" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B161" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C161" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D161" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E161" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F161" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G161" s="3"/>
-      <c r="H161" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B162" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C162" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="F162" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G162" s="3"/>
-      <c r="H162" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B163" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C163" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="D163" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="F163" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="G163" s="3"/>
-      <c r="H163" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
-      <c r="A164" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C164" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F164" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="G164" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="H164" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C165" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="F165" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C166" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D166" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E166" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F166" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G166" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C167" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F167" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G167" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H167" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C168" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="F168" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G168" s="3"/>
-      <c r="H168" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C169" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D169" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F169" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G169" s="3"/>
-      <c r="H169" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8">
-      <c r="A170" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C170" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D170" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E170" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="F170" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G170" s="3"/>
-      <c r="H170" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
-      <c r="A171" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B171" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F171" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8">
-      <c r="A172" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B172" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D172" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E172" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="F172" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="G172" s="3"/>
-      <c r="H172" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8">
-      <c r="A173" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C173" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F173" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="G173" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="H173" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
-      <c r="A174" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C174" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="D174" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E174" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F174" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G174" s="3"/>
-      <c r="H174" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
-      <c r="A175" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C175" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F175" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="G175" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="H175" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
-      <c r="A176" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C176" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E176" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="F176" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G176" s="3"/>
-      <c r="H176" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8">
-      <c r="A177" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C177" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E177" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="F177" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G177" s="3"/>
-      <c r="H177" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
-      <c r="A178" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C178" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D178" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E178" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F178" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="G178" s="3"/>
-      <c r="H178" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8">
-      <c r="A179" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B179" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E179" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="G179" s="3"/>
-      <c r="H179" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8">
-      <c r="A180" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C180" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E180" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G180" s="3"/>
-      <c r="H180" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
-      <c r="A181" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B181" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C181" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8">
-      <c r="A182" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C182" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="G182" s="3"/>
-      <c r="H182" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8">
-      <c r="A183" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B183" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C183" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E183" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="G183" s="3"/>
-      <c r="H183" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8">
-      <c r="A184" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B184" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C184" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E184" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="G184" s="3"/>
-      <c r="H184" s="3" t="s">
-        <v>600</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
-  <conditionalFormatting sqref="H2:H184">
+  <conditionalFormatting sqref="H2:H155">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>H2="대기"</formula>
     </cfRule>
@@ -6684,7 +5982,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="H2:H184" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="H2:H155" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"대기,완료,보류"</formula1>
     </dataValidation>
   </dataValidations>

--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479AC064-BF30-4D72-A107-8666625EA417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33197C67-536D-4F68-87CA-BF148D277839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="216">
   <si>
     <t>차량명</t>
   </si>
@@ -617,6 +617,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>~19년</t>
     </r>
@@ -734,6 +736,8 @@
       <rPr>
         <sz val="11"/>
         <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
       </rPr>
       <t>년</t>
     </r>
@@ -754,6 +758,37 @@
   </si>
   <si>
     <t>AG60</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>그랜저 IG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 3.3</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜저 IG 2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGM70</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1116,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H161"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1426,19 +1461,16 @@
         <v>25</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
+        <v>212</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
+        <v>214</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1452,10 +1484,10 @@
         <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E13" t="s">
-        <v>26</v>
+        <v>180</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>187</v>
@@ -1475,16 +1507,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1501,16 +1533,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1526,17 +1558,17 @@
       <c r="B16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>208</v>
+      <c r="C16" t="s">
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E16" t="s">
         <v>32</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1552,17 +1584,17 @@
       <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17" t="s">
-        <v>31</v>
+      <c r="C17" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
         <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1579,16 +1611,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1605,16 +1637,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1634,7 +1666,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E20" t="s">
         <v>36</v>
@@ -1657,13 +1689,13 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>179</v>
@@ -1686,7 +1718,7 @@
         <v>37</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E22" t="s">
         <v>38</v>
@@ -1706,22 +1738,22 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
+      </c>
+      <c r="G23" t="s">
+        <v>11</v>
       </c>
       <c r="H23" t="s">
         <v>12</v>
@@ -1738,7 +1770,7 @@
         <v>41</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E24" t="s">
         <v>42</v>
@@ -1763,17 +1795,17 @@
       <c r="C25" t="s">
         <v>41</v>
       </c>
-      <c r="D25" t="s">
-        <v>19</v>
+      <c r="D25" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G25" t="s">
-        <v>11</v>
+        <v>191</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1787,19 +1819,19 @@
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>181</v>
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
       </c>
       <c r="H26" t="s">
         <v>12</v>
@@ -1816,16 +1848,16 @@
         <v>45</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
         <v>46</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1842,16 +1874,16 @@
         <v>45</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G28" t="s">
-        <v>11</v>
+        <v>191</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1865,19 +1897,19 @@
         <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>185</v>
+        <v>177</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -1894,7 +1926,7 @@
         <v>48</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E30" t="s">
         <v>49</v>
@@ -1920,16 +1952,16 @@
         <v>48</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E31" t="s">
         <v>49</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G31" t="s">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1943,19 +1975,19 @@
         <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1972,7 +2004,7 @@
         <v>50</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E33" t="s">
         <v>51</v>
@@ -1998,16 +2030,16 @@
         <v>50</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E34" t="s">
         <v>51</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G34" t="s">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -2021,19 +2053,19 @@
         <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -2050,7 +2082,7 @@
         <v>52</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E36" t="s">
         <v>53</v>
@@ -2076,16 +2108,16 @@
         <v>52</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
         <v>53</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2099,19 +2131,19 @@
         <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
       </c>
       <c r="H38" t="s">
         <v>12</v>
@@ -2125,19 +2157,19 @@
         <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="H39" t="s">
         <v>12</v>
@@ -2154,16 +2186,16 @@
         <v>56</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E40" t="s">
         <v>57</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="G40" t="s">
-        <v>11</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -2174,19 +2206,19 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E41" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2206,13 +2238,13 @@
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E42" t="s">
         <v>60</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2229,16 +2261,16 @@
         <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -2258,13 +2290,13 @@
         <v>45</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
         <v>61</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2284,13 +2316,13 @@
         <v>45</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -2307,19 +2339,19 @@
         <v>59</v>
       </c>
       <c r="C46" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>189</v>
+      <c r="G46" t="s">
+        <v>11</v>
       </c>
       <c r="H46" t="s">
         <v>12</v>
@@ -2336,16 +2368,16 @@
         <v>48</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
         <v>62</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="G47" t="s">
-        <v>11</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
@@ -2359,19 +2391,19 @@
         <v>59</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G48" s="1" t="s">
         <v>189</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
       </c>
       <c r="H48" t="s">
         <v>12</v>
@@ -2388,16 +2420,16 @@
         <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E49" t="s">
         <v>64</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="G49" t="s">
-        <v>11</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
@@ -2411,16 +2443,16 @@
         <v>59</v>
       </c>
       <c r="C50" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2440,13 +2472,13 @@
         <v>65</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E51" t="s">
         <v>66</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2463,13 +2495,13 @@
         <v>59</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E52" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>197</v>
@@ -2492,7 +2524,7 @@
         <v>69</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="E53" t="s">
         <v>70</v>
@@ -2518,7 +2550,7 @@
         <v>69</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E54" t="s">
         <v>70</v>
@@ -2538,19 +2570,19 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C55" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E55" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2570,13 +2602,13 @@
         <v>41</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E56" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2596,13 +2628,13 @@
         <v>41</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E57" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2619,16 +2651,16 @@
         <v>71</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2648,13 +2680,13 @@
         <v>76</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E59" t="s">
         <v>77</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2674,13 +2706,13 @@
         <v>76</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2697,16 +2729,16 @@
         <v>71</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2726,13 +2758,13 @@
         <v>29</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E62" t="s">
         <v>79</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2778,7 +2810,7 @@
         <v>29</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E64" t="s">
         <v>79</v>
@@ -2800,17 +2832,17 @@
       <c r="B65" t="s">
         <v>71</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>186</v>
+      <c r="C65" t="s">
+        <v>29</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2826,17 +2858,17 @@
       <c r="B66" t="s">
         <v>71</v>
       </c>
-      <c r="C66" t="s">
-        <v>81</v>
+      <c r="C66" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E66" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2856,13 +2888,13 @@
         <v>81</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
         <v>82</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2882,7 +2914,7 @@
         <v>81</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E68" t="s">
         <v>82</v>
@@ -2905,16 +2937,16 @@
         <v>71</v>
       </c>
       <c r="C69" t="s">
-        <v>83</v>
-      </c>
-      <c r="D69" t="s">
-        <v>72</v>
+        <v>81</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2934,7 +2966,7 @@
         <v>83</v>
       </c>
       <c r="D70" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E70" t="s">
         <v>84</v>
@@ -2957,13 +2989,13 @@
         <v>71</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D71" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>179</v>
@@ -2986,7 +3018,7 @@
         <v>85</v>
       </c>
       <c r="D72" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E72" t="s">
         <v>86</v>
@@ -3012,7 +3044,7 @@
         <v>85</v>
       </c>
       <c r="D73" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E73" t="s">
         <v>86</v>
@@ -3035,16 +3067,16 @@
         <v>71</v>
       </c>
       <c r="C74" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D74" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3061,16 +3093,16 @@
         <v>71</v>
       </c>
       <c r="C75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E75" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3090,7 +3122,7 @@
         <v>89</v>
       </c>
       <c r="D76" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="E76" t="s">
         <v>90</v>
@@ -3116,7 +3148,7 @@
         <v>89</v>
       </c>
       <c r="D77" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E77" t="s">
         <v>90</v>
@@ -3142,7 +3174,7 @@
         <v>89</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="E78" t="s">
         <v>90</v>
@@ -3162,22 +3194,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C79" t="s">
-        <v>92</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>180</v>
+        <v>89</v>
+      </c>
+      <c r="D79" t="s">
+        <v>63</v>
       </c>
       <c r="E79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3194,7 +3226,7 @@
         <v>92</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E80" t="s">
         <v>93</v>
@@ -3243,13 +3275,13 @@
         <v>91</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E82" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>187</v>
@@ -3272,7 +3304,7 @@
         <v>94</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E83" t="s">
         <v>95</v>
@@ -3295,13 +3327,13 @@
         <v>91</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>187</v>
@@ -3324,7 +3356,7 @@
         <v>96</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E85" t="s">
         <v>91</v>
@@ -3344,22 +3376,22 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E86" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H86" t="s">
         <v>12</v>
@@ -3376,16 +3408,16 @@
         <v>41</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E87" t="s">
         <v>98</v>
       </c>
       <c r="F87" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G87" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="G87" t="s">
-        <v>11</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -3402,13 +3434,13 @@
         <v>41</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3425,16 +3457,16 @@
         <v>97</v>
       </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3454,13 +3486,13 @@
         <v>45</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E90" t="s">
         <v>100</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3480,13 +3512,13 @@
         <v>45</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E91" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
@@ -3503,16 +3535,16 @@
         <v>97</v>
       </c>
       <c r="C92" t="s">
-        <v>102</v>
+        <v>45</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E92" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3532,7 +3564,7 @@
         <v>102</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E93" t="s">
         <v>103</v>
@@ -3555,16 +3587,16 @@
         <v>97</v>
       </c>
       <c r="C94" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E94" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3584,7 +3616,7 @@
         <v>52</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E95" t="s">
         <v>104</v>
@@ -3607,13 +3639,13 @@
         <v>97</v>
       </c>
       <c r="C96" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E96" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>192</v>
@@ -3636,7 +3668,7 @@
         <v>58</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E97" t="s">
         <v>105</v>
@@ -3656,22 +3688,22 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E98" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
       </c>
       <c r="H98" t="s">
         <v>12</v>
@@ -3688,16 +3720,16 @@
         <v>107</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E99" t="s">
         <v>108</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G99" t="s">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -3711,19 +3743,19 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E100" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
+      </c>
+      <c r="G100" t="s">
+        <v>11</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -3740,16 +3772,16 @@
         <v>109</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E101" t="s">
         <v>110</v>
       </c>
       <c r="F101" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G101" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="G101" t="s">
-        <v>11</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -3763,19 +3795,19 @@
         <v>106</v>
       </c>
       <c r="C102" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E102" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G102" s="1" t="s">
         <v>185</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
       </c>
       <c r="H102" t="s">
         <v>12</v>
@@ -3792,16 +3824,16 @@
         <v>111</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E103" t="s">
         <v>112</v>
       </c>
       <c r="F103" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G103" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="G103" t="s">
-        <v>11</v>
       </c>
       <c r="H103" t="s">
         <v>12</v>
@@ -3815,16 +3847,16 @@
         <v>106</v>
       </c>
       <c r="C104" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E104" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -3844,13 +3876,13 @@
         <v>113</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E105" t="s">
         <v>106</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3867,16 +3899,16 @@
         <v>106</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E106" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3896,13 +3928,13 @@
         <v>114</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E107" t="s">
         <v>115</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3916,16 +3948,16 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>195</v>
+        <v>183</v>
+      </c>
+      <c r="E108" t="s">
+        <v>115</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>179</v>
@@ -3948,13 +3980,13 @@
         <v>117</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>195</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -3971,16 +4003,16 @@
         <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E110" t="s">
-        <v>116</v>
+        <v>183</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4000,7 +4032,7 @@
         <v>111</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="E111" t="s">
         <v>116</v>
@@ -4020,16 +4052,16 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C112" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E112" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>179</v>
@@ -4052,13 +4084,13 @@
         <v>117</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E113" t="s">
         <v>122</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4075,16 +4107,16 @@
         <v>121</v>
       </c>
       <c r="C114" t="s">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4104,13 +4136,13 @@
         <v>52</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="E115" t="s">
         <v>121</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="G115" t="s">
         <v>11</v>
@@ -4124,22 +4156,22 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E116" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
       </c>
       <c r="H116" t="s">
         <v>12</v>
@@ -4150,22 +4182,22 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E117" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G117" t="s">
-        <v>11</v>
+        <v>198</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4182,13 +4214,13 @@
         <v>126</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E118" t="s">
         <v>125</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -4202,19 +4234,19 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E119" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G119" t="s">
         <v>11</v>
@@ -4234,13 +4266,13 @@
         <v>128</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E120" t="s">
         <v>129</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
@@ -4254,22 +4286,22 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E121" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>190</v>
+        <v>179</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4283,13 +4315,13 @@
         <v>130</v>
       </c>
       <c r="C122" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E122" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>193</v>
@@ -4306,22 +4338,22 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C123" t="s">
-        <v>133</v>
+        <v>87</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E123" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G123" t="s">
-        <v>11</v>
+        <v>193</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H123" t="s">
         <v>12</v>
@@ -4338,16 +4370,16 @@
         <v>133</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E124" t="s">
         <v>134</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="G124" t="s">
+        <v>11</v>
       </c>
       <c r="H124" t="s">
         <v>12</v>
@@ -4361,19 +4393,19 @@
         <v>132</v>
       </c>
       <c r="C125" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="E125" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="G125" t="s">
-        <v>11</v>
+        <v>192</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="H125" t="s">
         <v>12</v>
@@ -4390,16 +4422,16 @@
         <v>135</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E126" t="s">
         <v>136</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
+      </c>
+      <c r="G126" t="s">
+        <v>11</v>
       </c>
       <c r="H126" t="s">
         <v>12</v>
@@ -4410,22 +4442,22 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C127" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E127" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G127" t="s">
-        <v>11</v>
+        <v>192</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="H127" t="s">
         <v>12</v>
@@ -4442,7 +4474,7 @@
         <v>92</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E128" t="s">
         <v>138</v>
@@ -4468,7 +4500,7 @@
         <v>92</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E129" t="s">
         <v>138</v>
@@ -4491,13 +4523,13 @@
         <v>137</v>
       </c>
       <c r="C130" t="s">
-        <v>139</v>
-      </c>
-      <c r="D130" t="s">
-        <v>16</v>
+        <v>92</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="E130" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>177</v>
@@ -4520,7 +4552,7 @@
         <v>139</v>
       </c>
       <c r="D131" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E131" t="s">
         <v>137</v>
@@ -4546,7 +4578,7 @@
         <v>139</v>
       </c>
       <c r="D132" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="E132" t="s">
         <v>137</v>
@@ -4566,19 +4598,19 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C133" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D133" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="E133" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4598,7 +4630,7 @@
         <v>141</v>
       </c>
       <c r="D134" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E134" t="s">
         <v>140</v>
@@ -4618,19 +4650,19 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C135" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="D135" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="E135" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -4647,13 +4679,13 @@
         <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="D136" t="s">
         <v>119</v>
       </c>
       <c r="E136" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>191</v>
@@ -4670,16 +4702,16 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C137" t="s">
-        <v>92</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>202</v>
+        <v>144</v>
+      </c>
+      <c r="D137" t="s">
+        <v>119</v>
       </c>
       <c r="E137" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>191</v>
@@ -4699,13 +4731,13 @@
         <v>145</v>
       </c>
       <c r="C138" t="s">
-        <v>94</v>
-      </c>
-      <c r="D138" t="s">
-        <v>119</v>
+        <v>92</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="E138" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>191</v>
@@ -4722,16 +4754,16 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>92</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>202</v>
+        <v>94</v>
+      </c>
+      <c r="D139" t="s">
+        <v>119</v>
       </c>
       <c r="E139" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>191</v>
@@ -4748,19 +4780,19 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C140" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="E140" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="G140" t="s">
         <v>11</v>
@@ -4774,22 +4806,22 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C141" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="G141" t="s">
+        <v>11</v>
       </c>
       <c r="H141" t="s">
         <v>12</v>
@@ -4806,16 +4838,16 @@
         <v>152</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E142" t="s">
         <v>153</v>
       </c>
       <c r="F142" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G142" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="H142" t="s">
         <v>12</v>
@@ -4826,22 +4858,22 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C143" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E143" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G143" t="s">
-        <v>11</v>
+        <v>185</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H143" t="s">
         <v>12</v>
@@ -4855,16 +4887,16 @@
         <v>154</v>
       </c>
       <c r="C144" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E144" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -4881,16 +4913,16 @@
         <v>154</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E145" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -4907,13 +4939,13 @@
         <v>154</v>
       </c>
       <c r="C146" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>180</v>
       </c>
       <c r="E146" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>179</v>
@@ -4930,19 +4962,19 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C147" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E147" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
@@ -4959,16 +4991,16 @@
         <v>160</v>
       </c>
       <c r="C148" t="s">
-        <v>163</v>
-      </c>
-      <c r="D148" t="s">
-        <v>161</v>
+        <v>118</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="E148" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -4982,19 +5014,19 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C149" t="s">
-        <v>41</v>
+        <v>163</v>
       </c>
       <c r="D149" t="s">
-        <v>43</v>
+        <v>161</v>
       </c>
       <c r="E149" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G149" t="s">
         <v>11</v>
@@ -5014,13 +5046,13 @@
         <v>41</v>
       </c>
       <c r="D150" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E150" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="G150" t="s">
         <v>11</v>
@@ -5040,10 +5072,10 @@
         <v>41</v>
       </c>
       <c r="D151" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>177</v>
@@ -5063,19 +5095,19 @@
         <v>164</v>
       </c>
       <c r="C152" t="s">
-        <v>45</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>180</v>
+        <v>41</v>
+      </c>
+      <c r="D152" t="s">
+        <v>119</v>
       </c>
       <c r="E152" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>190</v>
+        <v>177</v>
+      </c>
+      <c r="G152" t="s">
+        <v>11</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5092,16 +5124,16 @@
         <v>45</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E153" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G153" t="s">
-        <v>11</v>
+        <v>191</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H153" t="s">
         <v>12</v>
@@ -5115,19 +5147,19 @@
         <v>164</v>
       </c>
       <c r="C154" t="s">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E154" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G154" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
+      </c>
+      <c r="G154" t="s">
+        <v>11</v>
       </c>
       <c r="H154" t="s">
         <v>12</v>
@@ -5144,7 +5176,7 @@
         <v>170</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E155" t="s">
         <v>164</v>
@@ -5167,19 +5199,19 @@
         <v>164</v>
       </c>
       <c r="C156" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E156" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G156" t="s">
-        <v>11</v>
+        <v>191</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="H156" t="s">
         <v>12</v>
@@ -5193,13 +5225,13 @@
         <v>164</v>
       </c>
       <c r="C157" t="s">
-        <v>173</v>
-      </c>
-      <c r="D157" t="s">
-        <v>119</v>
+        <v>171</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="E157" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>198</v>
@@ -5216,19 +5248,19 @@
         <v>7</v>
       </c>
       <c r="B158" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C158" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="D158" t="s">
-        <v>18</v>
+        <v>119</v>
       </c>
       <c r="E158" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G158" t="s">
         <v>11</v>
@@ -5248,7 +5280,7 @@
         <v>120</v>
       </c>
       <c r="D159" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="E159" t="s">
         <v>175</v>
@@ -5274,7 +5306,7 @@
         <v>120</v>
       </c>
       <c r="D160" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E160" t="s">
         <v>175</v>
@@ -5286,6 +5318,32 @@
         <v>11</v>
       </c>
       <c r="H160" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
+      <c r="A161" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" t="s">
+        <v>175</v>
+      </c>
+      <c r="C161" t="s">
+        <v>120</v>
+      </c>
+      <c r="D161" t="s">
+        <v>68</v>
+      </c>
+      <c r="E161" t="s">
+        <v>175</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G161" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" t="s">
         <v>12</v>
       </c>
     </row>

--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33197C67-536D-4F68-87CA-BF148D277839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1597E0D1-65D6-4859-B6B9-642D955F6343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1287" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="207">
   <si>
     <t>차량명</t>
   </si>
@@ -61,27 +61,15 @@
     <t>대기</t>
   </si>
   <si>
-    <t>가솔린+전기 2WD</t>
-  </si>
-  <si>
     <t>더 뉴 그랜저 하이브리드 (GN7)</t>
   </si>
   <si>
     <t>22~26년</t>
   </si>
   <si>
-    <t>LPG 2WD</t>
-  </si>
-  <si>
     <t>그랜저 (GN7)</t>
   </si>
   <si>
-    <t>가솔린 4WD</t>
-  </si>
-  <si>
-    <t>가솔린+전기 1600cc</t>
-  </si>
-  <si>
     <t>그랜저 하이브리드 (GN7)</t>
   </si>
   <si>
@@ -91,9 +79,6 @@
     <t>더 뉴 그랜저 IG</t>
   </si>
   <si>
-    <t>가솔린 3300cc</t>
-  </si>
-  <si>
     <t>더 뉴 그랜저 IG 하이브리드</t>
   </si>
   <si>
@@ -103,12 +88,6 @@
     <t>그랜저 IG</t>
   </si>
   <si>
-    <t>가솔린 2400cc</t>
-  </si>
-  <si>
-    <t>가솔린 3000cc</t>
-  </si>
-  <si>
     <t>17~19년</t>
   </si>
   <si>
@@ -139,9 +118,6 @@
     <t>그랜저 뉴 럭셔리</t>
   </si>
   <si>
-    <t>가솔린 2000cc</t>
-  </si>
-  <si>
     <t>아반떼</t>
   </si>
   <si>
@@ -151,9 +127,6 @@
     <t>더 뉴 아반떼 (CN7)</t>
   </si>
   <si>
-    <t>가솔린 1600cc</t>
-  </si>
-  <si>
     <t>더 뉴 아반떼 하이브리드 (CN7)</t>
   </si>
   <si>
@@ -211,9 +184,6 @@
     <t>싼타페 TM</t>
   </si>
   <si>
-    <t>디젤 2000cc</t>
-  </si>
-  <si>
     <t>싼타페 더 프라임</t>
   </si>
   <si>
@@ -223,12 +193,6 @@
     <t>싼타페 DM</t>
   </si>
   <si>
-    <t>디젤 2WD</t>
-  </si>
-  <si>
-    <t>디젤 4WD</t>
-  </si>
-  <si>
     <t>05~12년</t>
   </si>
   <si>
@@ -238,15 +202,9 @@
     <t>쏘나타</t>
   </si>
   <si>
-    <t>LPG 2000cc</t>
-  </si>
-  <si>
     <t>쏘나타 디 엣지(DN8)</t>
   </si>
   <si>
-    <t>가솔린+전기 2000cc</t>
-  </si>
-  <si>
     <t>쏘나타 디 엣지 하이브리드(DN8)</t>
   </si>
   <si>
@@ -503,9 +461,6 @@
   </si>
   <si>
     <t>캐스퍼</t>
-  </si>
-  <si>
-    <t>가솔린 1000cc</t>
   </si>
   <si>
     <t>더 뉴 캐스퍼</t>
@@ -701,10 +656,6 @@
   </si>
   <si>
     <t>DIN100L</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>가솔린 1000cc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -761,6 +712,26 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>AGM70</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 3.3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">그랜저 IG </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>그랜저 IG</t>
     </r>
@@ -771,24 +742,32 @@
         <family val="3"/>
         <charset val="129"/>
       </rPr>
-      <t xml:space="preserve"> 3.3</t>
+      <t xml:space="preserve"> </t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve">가솔린+전기 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LPG </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">가솔린 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">디젤 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린+전기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>가솔린</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>그랜저 IG 2.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AGM70</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>대기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1151,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H161"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1166,7 +1145,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1201,13 +1180,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1227,13 +1206,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1253,13 +1232,13 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1276,16 +1255,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1302,16 +1281,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E6" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1328,16 +1307,16 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
+        <v>14</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1354,16 +1333,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -1380,19 +1359,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
@@ -1406,16 +1385,16 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1432,16 +1411,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>207</v>
+        <v>191</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1458,19 +1437,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1481,16 +1460,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1507,16 +1486,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1533,16 +1512,16 @@
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1559,16 +1538,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1585,16 +1564,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1611,16 +1590,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1637,16 +1616,16 @@
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1663,16 +1642,16 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1689,16 +1668,16 @@
         <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1715,16 +1694,16 @@
         <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -1741,16 +1720,16 @@
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E23" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1764,22 +1743,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1790,22 +1769,22 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1816,19 +1795,19 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1842,22 +1821,22 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C27" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1868,22 +1847,22 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1894,19 +1873,19 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C29" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1920,22 +1899,22 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E30" t="s">
         <v>40</v>
       </c>
-      <c r="C30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E30" t="s">
-        <v>49</v>
-      </c>
       <c r="F30" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H30" t="s">
         <v>12</v>
@@ -1946,22 +1925,22 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E31" t="s">
         <v>40</v>
       </c>
-      <c r="C31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E31" t="s">
-        <v>49</v>
-      </c>
       <c r="F31" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1972,19 +1951,19 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E32" t="s">
         <v>40</v>
       </c>
-      <c r="C32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E32" t="s">
-        <v>49</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -1998,22 +1977,22 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -2024,22 +2003,22 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -2050,19 +2029,19 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -2076,22 +2055,22 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -2102,22 +2081,22 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2128,19 +2107,19 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2154,22 +2133,22 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H39" t="s">
         <v>12</v>
@@ -2180,22 +2159,22 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -2206,19 +2185,19 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E41" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2232,19 +2211,19 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E42" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2258,19 +2237,19 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E43" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -2284,19 +2263,19 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E44" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2310,19 +2289,19 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E45" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -2336,19 +2315,19 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E46" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -2362,22 +2341,22 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
@@ -2388,19 +2367,19 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2414,22 +2393,22 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E49" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
@@ -2440,19 +2419,19 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2466,19 +2445,19 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E51" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2492,19 +2471,19 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2518,19 +2497,19 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2544,19 +2523,19 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="E54" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2570,19 +2549,19 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E55" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2596,19 +2575,19 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C56" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2622,19 +2601,19 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C57" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E57" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2648,19 +2627,19 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2674,19 +2653,19 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2700,19 +2679,19 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2726,19 +2705,19 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2752,19 +2731,19 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E62" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2778,19 +2757,19 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E63" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2804,19 +2783,19 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E64" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2830,19 +2809,19 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E65" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2856,19 +2835,19 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E66" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2882,19 +2861,19 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2908,19 +2887,19 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C68" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2934,19 +2913,19 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C69" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2960,19 +2939,19 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C70" t="s">
-        <v>83</v>
-      </c>
-      <c r="D70" t="s">
-        <v>72</v>
+        <v>69</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="E70" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2986,19 +2965,19 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C71" t="s">
-        <v>83</v>
-      </c>
-      <c r="D71" t="s">
-        <v>39</v>
+        <v>69</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="E71" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3012,19 +2991,19 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
+        <v>59</v>
+      </c>
+      <c r="C72" t="s">
         <v>71</v>
       </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="D72" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E72" t="s">
         <v>72</v>
       </c>
-      <c r="E72" t="s">
-        <v>86</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3038,19 +3017,19 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
+        <v>59</v>
+      </c>
+      <c r="C73" t="s">
         <v>71</v>
       </c>
-      <c r="C73" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" t="s">
-        <v>39</v>
+      <c r="D73" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -3064,19 +3043,19 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
-      </c>
-      <c r="D74" t="s">
-        <v>27</v>
+        <v>73</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="E74" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3090,19 +3069,19 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C75" t="s">
-        <v>87</v>
-      </c>
-      <c r="D75" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="E75" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3116,19 +3095,19 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C76" t="s">
-        <v>89</v>
-      </c>
-      <c r="D76" t="s">
-        <v>72</v>
+        <v>75</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="E76" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3142,19 +3121,19 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="C77" t="s">
-        <v>89</v>
-      </c>
-      <c r="D77" t="s">
-        <v>39</v>
+        <v>75</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="E77" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -3168,22 +3147,22 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C78" t="s">
-        <v>89</v>
-      </c>
-      <c r="D78" t="s">
-        <v>27</v>
+        <v>78</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G78" t="s">
-        <v>11</v>
+        <v>172</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -3194,22 +3173,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79" t="s">
-        <v>63</v>
+        <v>78</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="E79" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G79" t="s">
-        <v>11</v>
+        <v>172</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3220,22 +3199,22 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C80" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E80" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -3246,22 +3225,22 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C81" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="E81" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3272,22 +3251,22 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C82" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E82" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -3298,22 +3277,22 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C83" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E83" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -3324,22 +3303,22 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -3350,22 +3329,22 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E85" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H85" t="s">
         <v>12</v>
@@ -3376,22 +3355,22 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C86" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E86" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>189</v>
+        <v>172</v>
+      </c>
+      <c r="G86" t="s">
+        <v>11</v>
       </c>
       <c r="H86" t="s">
         <v>12</v>
@@ -3402,22 +3381,22 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C87" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E87" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>187</v>
+        <v>176</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -3428,19 +3407,19 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C88" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E88" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3454,19 +3433,19 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C89" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E89" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3480,19 +3459,19 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C90" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E90" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3506,19 +3485,19 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E91" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
@@ -3532,19 +3511,19 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E92" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3558,19 +3537,19 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E93" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
@@ -3584,19 +3563,19 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C94" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E94" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3610,19 +3589,19 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C95" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E95" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
@@ -3636,19 +3615,19 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E96" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -3662,22 +3641,22 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E97" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G97" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3688,19 +3667,19 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C98" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E98" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3714,22 +3693,22 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C99" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E99" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -3740,19 +3719,19 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C100" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E100" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -3766,22 +3745,22 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C101" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E101" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -3792,19 +3771,19 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C102" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E102" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -3818,22 +3797,22 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C103" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E103" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
       </c>
       <c r="H103" t="s">
         <v>12</v>
@@ -3844,19 +3823,19 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C104" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E104" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -3870,19 +3849,19 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C105" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E105" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3896,19 +3875,19 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C106" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E106" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3922,19 +3901,19 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D107" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E107" t="s">
-        <v>115</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3948,19 +3927,19 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C108" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E108" t="s">
-        <v>115</v>
+        <v>168</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -3974,19 +3953,19 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>195</v>
+        <v>173</v>
+      </c>
+      <c r="E109" t="s">
+        <v>102</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -4000,19 +3979,19 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>195</v>
+        <v>168</v>
+      </c>
+      <c r="E110" t="s">
+        <v>102</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4026,19 +4005,19 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C111" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="E111" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
@@ -4052,19 +4031,19 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C112" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E112" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4078,19 +4057,19 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C113" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E113" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4104,19 +4083,19 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C114" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E114" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4130,22 +4109,22 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C115" t="s">
-        <v>52</v>
+        <v>110</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E115" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G115" t="s">
-        <v>11</v>
+        <v>183</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="H115" t="s">
         <v>12</v>
@@ -4156,19 +4135,19 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="E116" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -4182,22 +4161,22 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C117" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E117" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4208,16 +4187,16 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C118" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E118" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>179</v>
@@ -4234,19 +4213,19 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="C119" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E119" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="G119" t="s">
         <v>11</v>
@@ -4260,22 +4239,22 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C120" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E120" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="G120" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4286,22 +4265,22 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E121" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G121" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4312,22 +4291,22 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="E122" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
+      </c>
+      <c r="G122" t="s">
+        <v>11</v>
       </c>
       <c r="H122" t="s">
         <v>12</v>
@@ -4338,22 +4317,22 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E123" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>193</v>
+        <v>177</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H123" t="s">
         <v>12</v>
@@ -4364,19 +4343,19 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C124" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E124" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
@@ -4390,22 +4369,22 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C125" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="E125" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="H125" t="s">
         <v>12</v>
@@ -4416,19 +4395,19 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C126" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E126" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -4442,22 +4421,22 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C127" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E127" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>201</v>
+        <v>162</v>
+      </c>
+      <c r="G127" t="s">
+        <v>11</v>
       </c>
       <c r="H127" t="s">
         <v>12</v>
@@ -4468,19 +4447,19 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C128" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E128" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4494,19 +4473,19 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C129" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E129" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G129" t="s">
         <v>11</v>
@@ -4520,19 +4499,19 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C130" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E130" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -4546,19 +4525,19 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="C131" t="s">
-        <v>139</v>
-      </c>
-      <c r="D131" t="s">
-        <v>16</v>
+        <v>125</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="E131" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4572,19 +4551,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
-        <v>139</v>
-      </c>
-      <c r="D132" t="s">
-        <v>13</v>
+        <v>127</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="E132" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4598,19 +4577,19 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D133" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E133" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4624,19 +4603,19 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C134" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D134" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="E134" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -4650,19 +4629,19 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C135" t="s">
-        <v>141</v>
-      </c>
-      <c r="D135" t="s">
-        <v>23</v>
+        <v>78</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="E135" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -4676,19 +4655,19 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C136" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D136" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E136" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -4702,19 +4681,19 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C137" t="s">
-        <v>144</v>
-      </c>
-      <c r="D137" t="s">
-        <v>119</v>
+        <v>78</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="E137" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4728,19 +4707,19 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C138" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -4754,22 +4733,22 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C139" t="s">
-        <v>94</v>
-      </c>
-      <c r="D139" t="s">
-        <v>119</v>
+        <v>138</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="E139" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G139" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H139" t="s">
         <v>12</v>
@@ -4780,22 +4759,22 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C140" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="E140" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G140" t="s">
-        <v>11</v>
+        <v>170</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H140" t="s">
         <v>12</v>
@@ -4806,19 +4785,19 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C141" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E141" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
@@ -4832,22 +4811,22 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C142" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E142" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
+      </c>
+      <c r="G142" t="s">
+        <v>11</v>
       </c>
       <c r="H142" t="s">
         <v>12</v>
@@ -4858,22 +4837,22 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C143" t="s">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E143" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
+      </c>
+      <c r="G143" t="s">
+        <v>11</v>
       </c>
       <c r="H143" t="s">
         <v>12</v>
@@ -4884,19 +4863,19 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C144" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E144" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -4910,19 +4889,19 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C145" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E145" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -4936,19 +4915,19 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C146" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="E146" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G146" t="s">
         <v>11</v>
@@ -4962,19 +4941,19 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="E147" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
@@ -4988,19 +4967,19 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C148" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E148" t="s">
+        <v>151</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -5014,19 +4993,19 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C149" t="s">
-        <v>163</v>
+        <v>33</v>
       </c>
       <c r="D149" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="E149" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="G149" t="s">
         <v>11</v>
@@ -5040,22 +5019,22 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C150" t="s">
-        <v>41</v>
-      </c>
-      <c r="D150" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="E150" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G150" t="s">
-        <v>11</v>
+        <v>176</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5066,19 +5045,19 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C151" t="s">
-        <v>41</v>
-      </c>
-      <c r="D151" t="s">
-        <v>19</v>
+        <v>36</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="E151" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G151" t="s">
         <v>11</v>
@@ -5092,22 +5071,22 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C152" t="s">
-        <v>41</v>
-      </c>
-      <c r="D152" t="s">
-        <v>119</v>
+        <v>155</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="E152" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G152" t="s">
-        <v>11</v>
+        <v>176</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5118,22 +5097,22 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C153" t="s">
-        <v>45</v>
+        <v>155</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E153" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="H153" t="s">
         <v>12</v>
@@ -5144,19 +5123,19 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C154" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E154" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="G154" t="s">
         <v>11</v>
@@ -5170,22 +5149,22 @@
         <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>180</v>
+        <v>158</v>
+      </c>
+      <c r="D155" t="s">
+        <v>105</v>
       </c>
       <c r="E155" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
+      </c>
+      <c r="G155" t="s">
+        <v>11</v>
       </c>
       <c r="H155" t="s">
         <v>12</v>
@@ -5196,22 +5175,22 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C156" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="E156" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
+      </c>
+      <c r="G156" t="s">
+        <v>11</v>
       </c>
       <c r="H156" t="s">
         <v>12</v>
@@ -5222,128 +5201,24 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C157" t="s">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="E157" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="G157" t="s">
         <v>11</v>
       </c>
       <c r="H157" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
-      <c r="A158" t="s">
-        <v>7</v>
-      </c>
-      <c r="B158" t="s">
-        <v>164</v>
-      </c>
-      <c r="C158" t="s">
-        <v>173</v>
-      </c>
-      <c r="D158" t="s">
-        <v>119</v>
-      </c>
-      <c r="E158" t="s">
-        <v>174</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G158" t="s">
-        <v>11</v>
-      </c>
-      <c r="H158" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
-      <c r="A159" t="s">
-        <v>7</v>
-      </c>
-      <c r="B159" t="s">
-        <v>175</v>
-      </c>
-      <c r="C159" t="s">
-        <v>120</v>
-      </c>
-      <c r="D159" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" t="s">
-        <v>175</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G159" t="s">
-        <v>11</v>
-      </c>
-      <c r="H159" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="A160" t="s">
-        <v>7</v>
-      </c>
-      <c r="B160" t="s">
-        <v>175</v>
-      </c>
-      <c r="C160" t="s">
-        <v>120</v>
-      </c>
-      <c r="D160" t="s">
-        <v>67</v>
-      </c>
-      <c r="E160" t="s">
-        <v>175</v>
-      </c>
-      <c r="F160" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G160" t="s">
-        <v>11</v>
-      </c>
-      <c r="H160" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="A161" t="s">
-        <v>7</v>
-      </c>
-      <c r="B161" t="s">
-        <v>175</v>
-      </c>
-      <c r="C161" t="s">
-        <v>120</v>
-      </c>
-      <c r="D161" t="s">
-        <v>68</v>
-      </c>
-      <c r="E161" t="s">
-        <v>175</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="G161" t="s">
-        <v>11</v>
-      </c>
-      <c r="H161" t="s">
         <v>12</v>
       </c>
     </row>

--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1597E0D1-65D6-4859-B6B9-642D955F6343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79093CDF-F6E0-45AD-AC7E-5A25B91B9DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="208">
   <si>
     <t>차량명</t>
   </si>
@@ -176,9 +176,6 @@
   </si>
   <si>
     <t>싼타페 (MX5)</t>
-  </si>
-  <si>
-    <t>더 뉴 싼타페</t>
   </si>
   <si>
     <t>싼타페 TM</t>
@@ -768,6 +765,25 @@
   </si>
   <si>
     <t>가솔린</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>더 뉴 싼타페</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> TM</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 싼타페 TM</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1145,7 +1161,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1180,13 +1196,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1206,13 +1222,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1232,13 +1248,13 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1258,13 +1274,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1284,13 +1300,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1310,13 +1326,13 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -1336,13 +1352,13 @@
         <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -1362,16 +1378,16 @@
         <v>17</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
@@ -1388,13 +1404,13 @@
         <v>17</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -1414,13 +1430,13 @@
         <v>20</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1440,16 +1456,16 @@
         <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1463,13 +1479,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1489,13 +1505,13 @@
         <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1515,13 +1531,13 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1541,13 +1557,13 @@
         <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E16" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1564,16 +1580,16 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1593,13 +1609,13 @@
         <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1619,13 +1635,13 @@
         <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1645,13 +1661,13 @@
         <v>28</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1671,13 +1687,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1697,13 +1713,13 @@
         <v>30</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -1723,13 +1739,13 @@
         <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
         <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -1749,16 +1765,16 @@
         <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1775,16 +1791,16 @@
         <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1801,13 +1817,13 @@
         <v>33</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
         <v>35</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G26" t="s">
         <v>11</v>
@@ -1827,16 +1843,16 @@
         <v>36</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
         <v>37</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1853,16 +1869,16 @@
         <v>36</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E28" t="s">
         <v>37</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1879,13 +1895,13 @@
         <v>36</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
         <v>11</v>
@@ -1905,16 +1921,16 @@
         <v>39</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E30" t="s">
         <v>40</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H30" t="s">
         <v>12</v>
@@ -1931,16 +1947,16 @@
         <v>39</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1957,13 +1973,13 @@
         <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
         <v>40</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G32" t="s">
         <v>11</v>
@@ -1983,16 +1999,16 @@
         <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
         <v>42</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -2009,16 +2025,16 @@
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
         <v>42</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -2035,13 +2051,13 @@
         <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G35" t="s">
         <v>11</v>
@@ -2061,16 +2077,16 @@
         <v>43</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -2087,16 +2103,16 @@
         <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
         <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2113,13 +2129,13 @@
         <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
         <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2139,16 +2155,16 @@
         <v>45</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E39" t="s">
         <v>46</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H39" t="s">
         <v>12</v>
@@ -2165,16 +2181,16 @@
         <v>47</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
         <v>48</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -2191,13 +2207,13 @@
         <v>47</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E41" t="s">
         <v>48</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2217,13 +2233,13 @@
         <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
         <v>51</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2243,13 +2259,13 @@
         <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E43" t="s">
         <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G43" t="s">
         <v>11</v>
@@ -2269,13 +2285,13 @@
         <v>36</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E44" t="s">
-        <v>52</v>
+        <v>164</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2295,13 +2311,13 @@
         <v>36</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E45" t="s">
-        <v>52</v>
+        <v>166</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G45" t="s">
         <v>11</v>
@@ -2321,13 +2337,13 @@
         <v>36</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E46" t="s">
-        <v>52</v>
+        <v>167</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -2347,16 +2363,16 @@
         <v>39</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
@@ -2373,13 +2389,13 @@
         <v>39</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2399,16 +2415,16 @@
         <v>41</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E49" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
@@ -2425,13 +2441,13 @@
         <v>41</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2448,16 +2464,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
+        <v>54</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E51" t="s">
         <v>55</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E51" t="s">
-        <v>56</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2474,16 +2490,16 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E52" t="s">
         <v>55</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="E52" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2500,16 +2516,16 @@
         <v>50</v>
       </c>
       <c r="C53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E53" t="s">
         <v>57</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E53" t="s">
-        <v>58</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2526,16 +2542,16 @@
         <v>50</v>
       </c>
       <c r="C54" t="s">
+        <v>56</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E54" t="s">
         <v>57</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E54" t="s">
-        <v>58</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2552,16 +2568,16 @@
         <v>50</v>
       </c>
       <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E55" t="s">
-        <v>58</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2575,19 +2591,19 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C56" t="s">
         <v>33</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E56" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2601,19 +2617,19 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
         <v>33</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2627,19 +2643,19 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C58" t="s">
         <v>33</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2653,19 +2669,19 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
+        <v>61</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" t="s">
         <v>62</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E59" t="s">
-        <v>63</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2679,19 +2695,19 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
+        <v>61</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" t="s">
-        <v>63</v>
-      </c>
       <c r="F60" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2705,19 +2721,19 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2731,19 +2747,19 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2757,19 +2773,19 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2783,19 +2799,19 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C64" t="s">
         <v>22</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2809,19 +2825,19 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C65" t="s">
         <v>22</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2835,19 +2851,19 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2861,19 +2877,19 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C67" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E67" t="s">
         <v>67</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E67" t="s">
-        <v>68</v>
-      </c>
       <c r="F67" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2887,19 +2903,19 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E68" t="s">
         <v>67</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E68" t="s">
-        <v>68</v>
-      </c>
       <c r="F68" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2913,19 +2929,19 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C69" t="s">
+        <v>66</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E69" t="s">
         <v>67</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" t="s">
-        <v>68</v>
-      </c>
       <c r="F69" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2939,19 +2955,19 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C70" t="s">
+        <v>68</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E70" t="s">
         <v>69</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E70" t="s">
-        <v>70</v>
-      </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2965,19 +2981,19 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E71" t="s">
         <v>69</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E71" t="s">
-        <v>70</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -2991,19 +3007,19 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C72" t="s">
+        <v>70</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" t="s">
         <v>71</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" t="s">
-        <v>72</v>
-      </c>
       <c r="F72" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3017,19 +3033,19 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C73" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E73" t="s">
         <v>71</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E73" t="s">
-        <v>72</v>
-      </c>
       <c r="F73" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -3043,19 +3059,19 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C74" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" t="s">
         <v>73</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E74" t="s">
-        <v>74</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G74" t="s">
         <v>11</v>
@@ -3069,19 +3085,19 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C75" t="s">
+        <v>74</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E75" t="s">
         <v>75</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E75" t="s">
-        <v>76</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G75" t="s">
         <v>11</v>
@@ -3095,19 +3111,19 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C76" t="s">
+        <v>74</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" t="s">
         <v>75</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E76" t="s">
-        <v>76</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G76" t="s">
         <v>11</v>
@@ -3121,19 +3137,19 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C77" t="s">
+        <v>74</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E77" t="s">
         <v>75</v>
       </c>
-      <c r="D77" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E77" t="s">
-        <v>76</v>
-      </c>
       <c r="F77" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G77" t="s">
         <v>11</v>
@@ -3147,22 +3163,22 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C78" t="s">
         <v>77</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E78" t="s">
         <v>78</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E78" t="s">
-        <v>79</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -3173,22 +3189,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" t="s">
         <v>77</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E79" t="s">
         <v>78</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E79" t="s">
-        <v>79</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3199,22 +3215,22 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
+        <v>76</v>
+      </c>
+      <c r="C80" t="s">
         <v>77</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E80" t="s">
         <v>78</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E80" t="s">
-        <v>79</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -3225,22 +3241,22 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
+        <v>79</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E81" t="s">
         <v>80</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E81" t="s">
-        <v>81</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3251,22 +3267,22 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" t="s">
+        <v>79</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E82" t="s">
         <v>80</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E82" t="s">
-        <v>81</v>
-      </c>
       <c r="F82" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -3277,22 +3293,22 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C83" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D83" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E83" t="s">
+        <v>76</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G83" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="E83" t="s">
-        <v>77</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -3303,22 +3319,22 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -3329,22 +3345,22 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H85" t="s">
         <v>12</v>
@@ -3355,19 +3371,19 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C86" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
@@ -3381,19 +3397,19 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C87" t="s">
         <v>33</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
@@ -3407,19 +3423,19 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C88" t="s">
         <v>36</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3433,19 +3449,19 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3459,19 +3475,19 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C90" t="s">
         <v>36</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E90" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3485,19 +3501,19 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C91" t="s">
+        <v>87</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E91" t="s">
         <v>88</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E91" t="s">
-        <v>89</v>
-      </c>
       <c r="F91" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
@@ -3511,19 +3527,19 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C92" t="s">
+        <v>87</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E92" t="s">
         <v>88</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E92" t="s">
-        <v>89</v>
-      </c>
       <c r="F92" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3537,19 +3553,19 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C93" t="s">
         <v>43</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E93" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G93" t="s">
         <v>11</v>
@@ -3563,19 +3579,19 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C94" t="s">
         <v>43</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3589,19 +3605,19 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C95" t="s">
         <v>49</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E95" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G95" t="s">
         <v>11</v>
@@ -3615,19 +3631,19 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C96" t="s">
         <v>49</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E96" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -3641,22 +3657,22 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
+        <v>91</v>
+      </c>
+      <c r="C97" t="s">
         <v>92</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E97" t="s">
         <v>93</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E97" t="s">
-        <v>94</v>
-      </c>
       <c r="F97" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3667,19 +3683,19 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
+        <v>91</v>
+      </c>
+      <c r="C98" t="s">
         <v>92</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E98" t="s">
         <v>93</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E98" t="s">
-        <v>94</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3693,22 +3709,22 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C99" t="s">
+        <v>94</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E99" t="s">
         <v>95</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E99" t="s">
-        <v>96</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -3719,19 +3735,19 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C100" t="s">
+        <v>94</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E100" t="s">
         <v>95</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E100" t="s">
-        <v>96</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -3745,22 +3761,22 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C101" t="s">
+        <v>96</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E101" t="s">
         <v>97</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E101" t="s">
-        <v>98</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -3771,19 +3787,19 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C102" t="s">
+        <v>96</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E102" t="s">
         <v>97</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E102" t="s">
-        <v>98</v>
-      </c>
       <c r="F102" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -3797,19 +3813,19 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E103" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
@@ -3823,19 +3839,19 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C104" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E104" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -3849,19 +3865,19 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C105" t="s">
+        <v>99</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E105" t="s">
         <v>100</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E105" t="s">
-        <v>101</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3875,19 +3891,19 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C106" t="s">
+        <v>99</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E106" t="s">
         <v>100</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E106" t="s">
-        <v>101</v>
-      </c>
       <c r="F106" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3901,19 +3917,19 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107" t="s">
         <v>102</v>
       </c>
-      <c r="C107" t="s">
-        <v>103</v>
-      </c>
       <c r="D107" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3927,19 +3943,19 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
+        <v>101</v>
+      </c>
+      <c r="C108" t="s">
         <v>102</v>
       </c>
-      <c r="C108" t="s">
-        <v>103</v>
-      </c>
       <c r="D108" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -3953,19 +3969,19 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C109" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E109" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -3979,19 +3995,19 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C110" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E110" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4005,19 +4021,19 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
+        <v>106</v>
+      </c>
+      <c r="C111" t="s">
+        <v>102</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E111" t="s">
         <v>107</v>
       </c>
-      <c r="C111" t="s">
-        <v>103</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E111" t="s">
-        <v>108</v>
-      </c>
       <c r="F111" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
@@ -4031,19 +4047,19 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
+        <v>106</v>
+      </c>
+      <c r="C112" t="s">
+        <v>102</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E112" t="s">
         <v>107</v>
       </c>
-      <c r="C112" t="s">
-        <v>103</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E112" t="s">
-        <v>108</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4057,19 +4073,19 @@
         <v>7</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C113" t="s">
         <v>43</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E113" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4083,19 +4099,19 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C114" t="s">
         <v>43</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E114" t="s">
+        <v>106</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="E114" t="s">
-        <v>107</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4109,22 +4125,22 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
+        <v>108</v>
+      </c>
+      <c r="C115" t="s">
         <v>109</v>
       </c>
-      <c r="C115" t="s">
-        <v>110</v>
-      </c>
       <c r="D115" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H115" t="s">
         <v>12</v>
@@ -4135,19 +4151,19 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" t="s">
         <v>111</v>
       </c>
-      <c r="C116" t="s">
-        <v>112</v>
-      </c>
       <c r="D116" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E116" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G116" t="s">
         <v>11</v>
@@ -4161,19 +4177,19 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" t="s">
         <v>111</v>
       </c>
-      <c r="C117" t="s">
-        <v>112</v>
-      </c>
       <c r="D117" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E117" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G117" t="s">
         <v>11</v>
@@ -4187,19 +4203,19 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
+        <v>112</v>
+      </c>
+      <c r="C118" t="s">
         <v>113</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E118" t="s">
         <v>114</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E118" t="s">
-        <v>115</v>
-      </c>
       <c r="F118" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -4213,19 +4229,19 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
+        <v>112</v>
+      </c>
+      <c r="C119" t="s">
         <v>113</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E119" t="s">
         <v>114</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E119" t="s">
-        <v>115</v>
-      </c>
       <c r="F119" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G119" t="s">
         <v>11</v>
@@ -4239,22 +4255,22 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
+        <v>115</v>
+      </c>
+      <c r="C120" t="s">
+        <v>81</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E120" t="s">
         <v>116</v>
       </c>
-      <c r="C120" t="s">
-        <v>82</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" t="s">
-        <v>117</v>
-      </c>
       <c r="F120" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4265,22 +4281,22 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C121" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E121" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4291,19 +4307,19 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
+        <v>117</v>
+      </c>
+      <c r="C122" t="s">
         <v>118</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E122" t="s">
         <v>119</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E122" t="s">
-        <v>120</v>
-      </c>
       <c r="F122" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
@@ -4317,22 +4333,22 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
+        <v>117</v>
+      </c>
+      <c r="C123" t="s">
         <v>118</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E123" t="s">
         <v>119</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E123" t="s">
-        <v>120</v>
-      </c>
       <c r="F123" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H123" t="s">
         <v>12</v>
@@ -4343,19 +4359,19 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C124" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E124" t="s">
         <v>121</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E124" t="s">
-        <v>122</v>
-      </c>
       <c r="F124" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
@@ -4369,22 +4385,22 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C125" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E125" t="s">
         <v>121</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E125" t="s">
-        <v>122</v>
-      </c>
       <c r="F125" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H125" t="s">
         <v>12</v>
@@ -4395,19 +4411,19 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
+        <v>122</v>
+      </c>
+      <c r="C126" t="s">
+        <v>77</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E126" t="s">
         <v>123</v>
       </c>
-      <c r="C126" t="s">
-        <v>78</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E126" t="s">
-        <v>124</v>
-      </c>
       <c r="F126" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -4421,19 +4437,19 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
+        <v>122</v>
+      </c>
+      <c r="C127" t="s">
+        <v>77</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E127" t="s">
         <v>123</v>
       </c>
-      <c r="C127" t="s">
-        <v>78</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E127" t="s">
-        <v>124</v>
-      </c>
       <c r="F127" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
@@ -4447,19 +4463,19 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
+        <v>122</v>
+      </c>
+      <c r="C128" t="s">
+        <v>77</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E128" t="s">
         <v>123</v>
       </c>
-      <c r="C128" t="s">
-        <v>78</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E128" t="s">
-        <v>124</v>
-      </c>
       <c r="F128" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4473,19 +4489,19 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C129" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E129" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G129" t="s">
         <v>11</v>
@@ -4499,19 +4515,19 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E130" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -4525,19 +4541,19 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C131" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E131" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4551,19 +4567,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
+        <v>125</v>
+      </c>
+      <c r="C132" t="s">
         <v>126</v>
       </c>
-      <c r="C132" t="s">
-        <v>127</v>
-      </c>
       <c r="D132" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E132" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4577,19 +4593,19 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
+        <v>127</v>
+      </c>
+      <c r="C133" t="s">
+        <v>103</v>
+      </c>
+      <c r="D133" t="s">
+        <v>104</v>
+      </c>
+      <c r="E133" t="s">
         <v>128</v>
       </c>
-      <c r="C133" t="s">
-        <v>104</v>
-      </c>
-      <c r="D133" t="s">
-        <v>105</v>
-      </c>
-      <c r="E133" t="s">
-        <v>129</v>
-      </c>
       <c r="F133" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4603,19 +4619,19 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E134" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -4629,19 +4645,19 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
+        <v>130</v>
+      </c>
+      <c r="C135" t="s">
+        <v>77</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E135" t="s">
         <v>131</v>
       </c>
-      <c r="C135" t="s">
-        <v>78</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E135" t="s">
-        <v>132</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G135" t="s">
         <v>11</v>
@@ -4655,19 +4671,19 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C136" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D136" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E136" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -4681,19 +4697,19 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C137" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E137" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4707,19 +4723,19 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
+        <v>133</v>
+      </c>
+      <c r="C138" t="s">
         <v>134</v>
       </c>
-      <c r="C138" t="s">
+      <c r="D138" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E138" t="s">
         <v>135</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E138" t="s">
-        <v>136</v>
-      </c>
       <c r="F138" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -4733,22 +4749,22 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
+        <v>136</v>
+      </c>
+      <c r="C139" t="s">
         <v>137</v>
       </c>
-      <c r="C139" t="s">
+      <c r="D139" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E139" t="s">
         <v>138</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E139" t="s">
-        <v>139</v>
-      </c>
       <c r="F139" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H139" t="s">
         <v>12</v>
@@ -4759,22 +4775,22 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
+        <v>136</v>
+      </c>
+      <c r="C140" t="s">
         <v>137</v>
       </c>
-      <c r="C140" t="s">
+      <c r="D140" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E140" t="s">
         <v>138</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E140" t="s">
-        <v>139</v>
-      </c>
       <c r="F140" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H140" t="s">
         <v>12</v>
@@ -4785,19 +4801,19 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
+        <v>139</v>
+      </c>
+      <c r="C141" t="s">
         <v>140</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E141" t="s">
         <v>141</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E141" t="s">
-        <v>142</v>
-      </c>
       <c r="F141" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
@@ -4811,19 +4827,19 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C142" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G142" t="s">
         <v>11</v>
@@ -4837,19 +4853,19 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C143" t="s">
         <v>24</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E143" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G143" t="s">
         <v>11</v>
@@ -4863,19 +4879,19 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C144" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -4889,19 +4905,19 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
+        <v>145</v>
+      </c>
+      <c r="C145" t="s">
+        <v>103</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E145" t="s">
         <v>146</v>
       </c>
-      <c r="C145" t="s">
-        <v>104</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E145" t="s">
-        <v>147</v>
-      </c>
       <c r="F145" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -4915,19 +4931,19 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C146" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E146" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G146" t="s">
         <v>11</v>
@@ -4941,19 +4957,19 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C147" t="s">
         <v>33</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E147" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
@@ -4967,19 +4983,19 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C148" t="s">
         <v>33</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E148" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G148" t="s">
         <v>11</v>
@@ -4993,19 +5009,19 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C149" t="s">
         <v>33</v>
       </c>
       <c r="D149" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E149" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G149" t="s">
         <v>11</v>
@@ -5019,22 +5035,22 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C150" t="s">
         <v>36</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5045,19 +5061,19 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C151" t="s">
         <v>36</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E151" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G151" t="s">
         <v>11</v>
@@ -5071,22 +5087,22 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C152" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E152" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5097,22 +5113,22 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C153" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E153" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H153" t="s">
         <v>12</v>
@@ -5123,19 +5139,19 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s">
+        <v>155</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E154" t="s">
         <v>156</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E154" t="s">
-        <v>157</v>
-      </c>
       <c r="F154" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G154" t="s">
         <v>11</v>
@@ -5149,19 +5165,19 @@
         <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C155" t="s">
+        <v>157</v>
+      </c>
+      <c r="D155" t="s">
+        <v>104</v>
+      </c>
+      <c r="E155" t="s">
         <v>158</v>
       </c>
-      <c r="D155" t="s">
-        <v>105</v>
-      </c>
-      <c r="E155" t="s">
-        <v>159</v>
-      </c>
       <c r="F155" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G155" t="s">
         <v>11</v>
@@ -5175,19 +5191,19 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C156" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E156" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G156" t="s">
         <v>11</v>
@@ -5201,19 +5217,19 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C157" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G157" t="s">
         <v>11</v>
@@ -5225,5 +5241,6 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79093CDF-F6E0-45AD-AC7E-5A25B91B9DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42459CCB-AF1A-406E-8021-DDAE57155CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="206">
   <si>
     <t>차량명</t>
   </si>
@@ -61,18 +61,12 @@
     <t>대기</t>
   </si>
   <si>
-    <t>더 뉴 그랜저 하이브리드 (GN7)</t>
-  </si>
-  <si>
     <t>22~26년</t>
   </si>
   <si>
     <t>그랜저 (GN7)</t>
   </si>
   <si>
-    <t>그랜저 하이브리드 (GN7)</t>
-  </si>
-  <si>
     <t>19~22년</t>
   </si>
   <si>
@@ -127,16 +121,10 @@
     <t>더 뉴 아반떼 (CN7)</t>
   </si>
   <si>
-    <t>더 뉴 아반떼 하이브리드 (CN7)</t>
-  </si>
-  <si>
     <t>20~23년</t>
   </si>
   <si>
     <t>아반떼 (CN7)</t>
-  </si>
-  <si>
-    <t>아반떼 하이브리드 (CN7)</t>
   </si>
   <si>
     <t>18~20년</t>
@@ -784,6 +772,14 @@
   </si>
   <si>
     <t>더 뉴 싼타페 TM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>싼타페 하이브리드 (MX5)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 싼타페 하이브리드 TM</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1146,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H153"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1161,7 +1157,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1196,13 +1192,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1222,13 +1218,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1245,16 +1241,16 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1271,16 +1267,16 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1297,16 +1293,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1323,19 +1319,19 @@
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" t="s">
-        <v>11</v>
+        <v>170</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
@@ -1349,16 +1345,16 @@
         <v>8</v>
       </c>
       <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -1375,19 +1371,19 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>171</v>
+        <v>186</v>
+      </c>
+      <c r="G9" t="s">
+        <v>11</v>
       </c>
       <c r="H9" t="s">
         <v>12</v>
@@ -1401,22 +1397,19 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
+        <v>192</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
+        <v>190</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1427,16 +1420,16 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" t="s">
-        <v>21</v>
+        <v>193</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1453,19 +1446,22 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>198</v>
+        <v>163</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>195</v>
+        <v>167</v>
+      </c>
+      <c r="G12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1479,13 +1475,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>199</v>
+        <v>162</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1502,16 +1498,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1527,17 +1523,17 @@
       <c r="B15" t="s">
         <v>8</v>
       </c>
-      <c r="C15" t="s">
-        <v>22</v>
+      <c r="C15" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1554,16 +1550,16 @@
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1579,17 +1575,17 @@
       <c r="B17" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>191</v>
+      <c r="C17" t="s">
+        <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>192</v>
+        <v>164</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1606,16 +1602,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1635,13 +1631,13 @@
         <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1661,13 +1657,13 @@
         <v>28</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1687,13 +1683,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1707,22 +1703,22 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G22" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H22" t="s">
         <v>12</v>
@@ -1733,22 +1729,22 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G23" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H23" t="s">
         <v>12</v>
@@ -1759,22 +1755,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1785,22 +1781,22 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1811,22 +1807,22 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>200</v>
+        <v>161</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G26" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H26" t="s">
         <v>12</v>
@@ -1837,22 +1833,22 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E27" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E27" t="s">
-        <v>37</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1863,22 +1859,22 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E28" t="s">
-        <v>37</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1889,22 +1885,22 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -1915,22 +1911,22 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E30" t="s">
+        <v>38</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E30" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H30" t="s">
         <v>12</v>
@@ -1941,22 +1937,22 @@
         <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1967,22 +1963,22 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
         <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E32" t="s">
         <v>40</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G32" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1993,22 +1989,22 @@
         <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="E33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -2019,22 +2015,22 @@
         <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -2045,22 +2041,22 @@
         <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
         <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G35" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -2071,22 +2067,22 @@
         <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
         <v>43</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -2097,22 +2093,22 @@
         <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E37" t="s">
         <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2123,19 +2119,19 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2149,22 +2145,22 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" t="s">
-        <v>46</v>
+        <v>162</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
       </c>
       <c r="H39" t="s">
         <v>12</v>
@@ -2175,22 +2171,22 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40" t="s">
-        <v>48</v>
+        <v>160</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
+      </c>
+      <c r="G40" t="s">
+        <v>11</v>
       </c>
       <c r="H40" t="s">
         <v>12</v>
@@ -2201,19 +2197,19 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C41" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E41" t="s">
-        <v>48</v>
+        <v>162</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2227,19 +2223,19 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C42" t="s">
         <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" t="s">
-        <v>51</v>
+        <v>163</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2253,22 +2249,22 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G43" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H43" t="s">
         <v>12</v>
@@ -2279,19 +2275,19 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>206</v>
+        <v>163</v>
+      </c>
+      <c r="E44" t="s">
+        <v>48</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2305,22 +2301,22 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>206</v>
+        <v>160</v>
+      </c>
+      <c r="E45" t="s">
+        <v>49</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G45" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H45" t="s">
         <v>12</v>
@@ -2331,19 +2327,19 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C46" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>207</v>
+        <v>163</v>
+      </c>
+      <c r="E46" t="s">
+        <v>49</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -2357,22 +2353,22 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" t="s">
-        <v>39</v>
-      </c>
       <c r="D47" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
       </c>
       <c r="H47" t="s">
         <v>12</v>
@@ -2383,19 +2379,19 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" t="s">
         <v>50</v>
       </c>
-      <c r="C48" t="s">
-        <v>39</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2409,22 +2405,22 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="E49" t="s">
         <v>53</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
+      </c>
+      <c r="G49" t="s">
+        <v>11</v>
       </c>
       <c r="H49" t="s">
         <v>12</v>
@@ -2435,19 +2431,19 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C50" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2461,19 +2457,19 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2487,19 +2483,19 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E52" t="s">
         <v>55</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2513,19 +2509,19 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2539,19 +2535,19 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E54" t="s">
         <v>56</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E54" t="s">
-        <v>57</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2565,19 +2561,19 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2591,19 +2587,19 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" t="s">
         <v>58</v>
       </c>
-      <c r="C56" t="s">
-        <v>33</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E56" t="s">
-        <v>59</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2617,19 +2613,19 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E57" t="s">
         <v>59</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2643,19 +2639,19 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E58" t="s">
         <v>60</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2669,19 +2665,19 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E59" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2695,19 +2691,19 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2721,19 +2717,19 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E61" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2747,19 +2743,19 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>58</v>
-      </c>
-      <c r="C62" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E62" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2773,19 +2769,19 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2799,19 +2795,19 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2825,19 +2821,19 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D65" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E65" t="s">
+        <v>63</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E65" t="s">
-        <v>64</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2851,19 +2847,19 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>170</v>
+        <v>54</v>
+      </c>
+      <c r="C66" t="s">
+        <v>64</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="E66" t="s">
         <v>65</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2877,19 +2873,19 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="E67" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2903,19 +2899,19 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C68" t="s">
         <v>66</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="E68" t="s">
         <v>67</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2929,19 +2925,19 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C69" t="s">
         <v>66</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="E69" t="s">
         <v>67</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2955,19 +2951,19 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C70" t="s">
         <v>68</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E70" t="s">
         <v>69</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2981,19 +2977,19 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E71" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3007,19 +3003,19 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C72" t="s">
         <v>70</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E72" t="s">
         <v>71</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G72" t="s">
         <v>11</v>
@@ -3033,19 +3029,19 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C73" t="s">
         <v>70</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E73" t="s">
         <v>71</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G73" t="s">
         <v>11</v>
@@ -3059,22 +3055,22 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E74" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G74" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H74" t="s">
         <v>12</v>
@@ -3085,22 +3081,22 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C75" t="s">
+        <v>73</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E75" t="s">
         <v>74</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E75" t="s">
-        <v>75</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G75" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H75" t="s">
         <v>12</v>
@@ -3111,22 +3107,22 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C76" t="s">
+        <v>73</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E76" t="s">
         <v>74</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E76" t="s">
-        <v>75</v>
-      </c>
       <c r="F76" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G76" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H76" t="s">
         <v>12</v>
@@ -3137,22 +3133,22 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="E77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G77" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="H77" t="s">
         <v>12</v>
@@ -3163,22 +3159,22 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
+        <v>72</v>
+      </c>
+      <c r="C78" t="s">
+        <v>75</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E78" t="s">
         <v>76</v>
       </c>
-      <c r="C78" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" t="s">
-        <v>78</v>
-      </c>
       <c r="F78" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -3189,22 +3185,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C79" t="s">
         <v>77</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3215,22 +3211,22 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C80" t="s">
         <v>77</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -3241,22 +3237,22 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
+        <v>31</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E81" t="s">
         <v>79</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E81" t="s">
-        <v>80</v>
-      </c>
       <c r="F81" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3267,22 +3263,22 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
+        <v>31</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E82" t="s">
         <v>79</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="F82" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="E82" t="s">
-        <v>80</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>173</v>
+      <c r="G82" t="s">
+        <v>11</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -3293,22 +3289,22 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C83" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E83" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>173</v>
+      <c r="G83" t="s">
+        <v>11</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -3319,22 +3315,22 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C84" t="s">
+        <v>33</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E84" t="s">
         <v>81</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E84" t="s">
-        <v>76</v>
-      </c>
       <c r="F84" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -3345,22 +3341,22 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C85" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E85" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
+      </c>
+      <c r="G85" t="s">
+        <v>11</v>
       </c>
       <c r="H85" t="s">
         <v>12</v>
@@ -3371,16 +3367,16 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C86" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E86" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>171</v>
@@ -3397,19 +3393,19 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E87" t="s">
         <v>84</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
@@ -3423,19 +3419,19 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C88" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3449,19 +3445,19 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C89" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E89" t="s">
         <v>85</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3475,19 +3471,19 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E90" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3501,19 +3497,19 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C91" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E91" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G91" t="s">
         <v>11</v>
@@ -3527,19 +3523,19 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C92" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E92" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3553,22 +3549,22 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C93" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E93" t="s">
         <v>89</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G93" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -3579,19 +3575,19 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C94" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E94" t="s">
         <v>89</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3605,22 +3601,22 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C95" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E95" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G95" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H95" t="s">
         <v>12</v>
@@ -3631,19 +3627,19 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C96" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E96" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -3657,22 +3653,22 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C97" t="s">
         <v>92</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E97" t="s">
         <v>93</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3683,19 +3679,19 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C98" t="s">
         <v>92</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E98" t="s">
         <v>93</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3709,22 +3705,22 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C99" t="s">
         <v>94</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E99" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -3735,19 +3731,19 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C100" t="s">
         <v>94</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E100" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -3761,22 +3757,22 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C101" t="s">
+        <v>95</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E101" t="s">
         <v>96</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E101" t="s">
-        <v>97</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
+      </c>
+      <c r="G101" t="s">
+        <v>11</v>
       </c>
       <c r="H101" t="s">
         <v>12</v>
@@ -3787,19 +3783,19 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C102" t="s">
+        <v>95</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E102" t="s">
         <v>96</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E102" t="s">
-        <v>97</v>
-      </c>
       <c r="F102" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -3813,19 +3809,19 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C103" t="s">
         <v>98</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E103" t="s">
-        <v>91</v>
+        <v>160</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
@@ -3839,19 +3835,19 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C104" t="s">
         <v>98</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E104" t="s">
-        <v>91</v>
+        <v>163</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -3865,19 +3861,19 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C105" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E105" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3891,19 +3887,19 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C106" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E106" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3917,19 +3913,19 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>179</v>
+        <v>160</v>
+      </c>
+      <c r="E107" t="s">
+        <v>103</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3943,19 +3939,19 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C108" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>179</v>
+        <v>163</v>
+      </c>
+      <c r="E108" t="s">
+        <v>103</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -3969,19 +3965,19 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E109" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G109" t="s">
         <v>11</v>
@@ -3995,19 +3991,19 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E110" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4021,22 +4017,22 @@
         <v>7</v>
       </c>
       <c r="B111" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C111" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E111" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G111" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -4050,16 +4046,16 @@
         <v>106</v>
       </c>
       <c r="C112" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E112" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4076,16 +4072,16 @@
         <v>106</v>
       </c>
       <c r="C113" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E113" t="s">
         <v>106</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4099,19 +4095,19 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C114" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="E114" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G114" t="s">
         <v>11</v>
@@ -4131,16 +4127,16 @@
         <v>109</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E115" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>177</v>
+        <v>159</v>
+      </c>
+      <c r="G115" t="s">
+        <v>11</v>
       </c>
       <c r="H115" t="s">
         <v>12</v>
@@ -4151,22 +4147,22 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E116" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G116" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H116" t="s">
         <v>12</v>
@@ -4177,22 +4173,22 @@
         <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C117" t="s">
+        <v>68</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E117" t="s">
         <v>111</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E117" t="s">
-        <v>110</v>
-      </c>
       <c r="F117" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G117" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4203,19 +4199,19 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C118" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E118" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -4229,22 +4225,22 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C119" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E119" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="G119" t="s">
-        <v>11</v>
+        <v>172</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4255,22 +4251,22 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C120" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
+      </c>
+      <c r="G120" t="s">
+        <v>11</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4281,22 +4277,22 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C121" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E121" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4307,19 +4303,19 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C122" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E122" t="s">
         <v>119</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
@@ -4333,22 +4329,22 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C123" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E123" t="s">
         <v>119</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>185</v>
+        <v>157</v>
+      </c>
+      <c r="G123" t="s">
+        <v>11</v>
       </c>
       <c r="H123" t="s">
         <v>12</v>
@@ -4359,19 +4355,19 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C124" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="E124" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
@@ -4385,22 +4381,22 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C125" t="s">
         <v>120</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="E125" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>185</v>
+        <v>157</v>
+      </c>
+      <c r="G125" t="s">
+        <v>11</v>
       </c>
       <c r="H125" t="s">
         <v>12</v>
@@ -4411,19 +4407,19 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C126" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="E126" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -4437,19 +4433,19 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="E127" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
@@ -4463,19 +4459,19 @@
         <v>7</v>
       </c>
       <c r="B128" t="s">
+        <v>121</v>
+      </c>
+      <c r="C128" t="s">
         <v>122</v>
       </c>
-      <c r="C128" t="s">
-        <v>77</v>
-      </c>
       <c r="D128" s="1" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E128" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4489,19 +4485,19 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C129" t="s">
+        <v>99</v>
+      </c>
+      <c r="D129" t="s">
+        <v>100</v>
+      </c>
+      <c r="E129" t="s">
         <v>124</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E129" t="s">
-        <v>122</v>
-      </c>
       <c r="F129" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G129" t="s">
         <v>11</v>
@@ -4515,19 +4511,19 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C130" t="s">
-        <v>124</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>204</v>
+        <v>125</v>
+      </c>
+      <c r="D130" t="s">
+        <v>100</v>
       </c>
       <c r="E130" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -4541,19 +4537,19 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="E131" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4567,19 +4563,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
+        <v>75</v>
+      </c>
+      <c r="D132" t="s">
+        <v>100</v>
+      </c>
+      <c r="E132" t="s">
         <v>126</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E132" t="s">
-        <v>125</v>
-      </c>
       <c r="F132" s="1" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4593,19 +4589,19 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
-      </c>
-      <c r="D133" t="s">
-        <v>104</v>
+        <v>73</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="E133" t="s">
         <v>128</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G133" t="s">
         <v>11</v>
@@ -4619,19 +4615,19 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C134" t="s">
-        <v>129</v>
-      </c>
-      <c r="D134" t="s">
-        <v>104</v>
+        <v>130</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="E134" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="G134" t="s">
         <v>11</v>
@@ -4645,22 +4641,22 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C135" t="s">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="E135" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G135" t="s">
-        <v>11</v>
+        <v>173</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="H135" t="s">
         <v>12</v>
@@ -4671,22 +4667,22 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C136" t="s">
-        <v>79</v>
-      </c>
-      <c r="D136" t="s">
-        <v>104</v>
+        <v>133</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G136" t="s">
-        <v>11</v>
+        <v>165</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H136" t="s">
         <v>12</v>
@@ -4697,19 +4693,19 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C137" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="E137" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4723,19 +4719,19 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C138" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E138" t="s">
         <v>135</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -4749,22 +4745,22 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C139" t="s">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E139" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>169</v>
+        <v>159</v>
+      </c>
+      <c r="G139" t="s">
+        <v>11</v>
       </c>
       <c r="H139" t="s">
         <v>12</v>
@@ -4775,22 +4771,22 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C140" t="s">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E140" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>174</v>
+        <v>159</v>
+      </c>
+      <c r="G140" t="s">
+        <v>11</v>
       </c>
       <c r="H140" t="s">
         <v>12</v>
@@ -4801,19 +4797,19 @@
         <v>7</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="G141" t="s">
         <v>11</v>
@@ -4827,19 +4823,19 @@
         <v>7</v>
       </c>
       <c r="B142" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C142" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E142" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G142" t="s">
         <v>11</v>
@@ -4853,19 +4849,19 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="E143" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G143" t="s">
         <v>11</v>
@@ -4879,19 +4875,19 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C144" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="E144" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -4905,19 +4901,19 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C145" t="s">
-        <v>103</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>164</v>
+        <v>31</v>
+      </c>
+      <c r="D145" t="s">
+        <v>100</v>
       </c>
       <c r="E145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -4931,22 +4927,22 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C146" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="E146" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G146" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H146" t="s">
         <v>12</v>
@@ -4957,19 +4953,19 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C147" t="s">
         <v>33</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>202</v>
+        <v>162</v>
       </c>
       <c r="E147" t="s">
         <v>149</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
@@ -4983,22 +4979,22 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C148" t="s">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="E148" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G148" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H148" t="s">
         <v>12</v>
@@ -5009,22 +5005,22 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C149" t="s">
-        <v>33</v>
-      </c>
-      <c r="D149" t="s">
-        <v>104</v>
+        <v>150</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="E149" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G149" t="s">
-        <v>11</v>
+        <v>171</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="H149" t="s">
         <v>12</v>
@@ -5035,22 +5031,22 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C150" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E150" t="s">
         <v>152</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
+      </c>
+      <c r="G150" t="s">
+        <v>11</v>
       </c>
       <c r="H150" t="s">
         <v>12</v>
@@ -5061,19 +5057,19 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C151" t="s">
-        <v>36</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>166</v>
+        <v>153</v>
+      </c>
+      <c r="D151" t="s">
+        <v>100</v>
       </c>
       <c r="E151" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G151" t="s">
         <v>11</v>
@@ -5087,22 +5083,22 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C152" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="E152" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
+      </c>
+      <c r="G152" t="s">
+        <v>11</v>
       </c>
       <c r="H152" t="s">
         <v>12</v>
@@ -5113,128 +5109,24 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C153" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
       <c r="E153" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
+      </c>
+      <c r="G153" t="s">
+        <v>11</v>
       </c>
       <c r="H153" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
-      <c r="A154" t="s">
-        <v>7</v>
-      </c>
-      <c r="B154" t="s">
-        <v>148</v>
-      </c>
-      <c r="C154" t="s">
-        <v>155</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E154" t="s">
-        <v>156</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G154" t="s">
-        <v>11</v>
-      </c>
-      <c r="H154" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
-      <c r="A155" t="s">
-        <v>7</v>
-      </c>
-      <c r="B155" t="s">
-        <v>148</v>
-      </c>
-      <c r="C155" t="s">
-        <v>157</v>
-      </c>
-      <c r="D155" t="s">
-        <v>104</v>
-      </c>
-      <c r="E155" t="s">
-        <v>158</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G155" t="s">
-        <v>11</v>
-      </c>
-      <c r="H155" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
-      <c r="A156" t="s">
-        <v>7</v>
-      </c>
-      <c r="B156" t="s">
-        <v>159</v>
-      </c>
-      <c r="C156" t="s">
-        <v>105</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E156" t="s">
-        <v>159</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G156" t="s">
-        <v>11</v>
-      </c>
-      <c r="H156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
-      <c r="A157" t="s">
-        <v>7</v>
-      </c>
-      <c r="B157" t="s">
-        <v>159</v>
-      </c>
-      <c r="C157" t="s">
-        <v>105</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E157" t="s">
-        <v>159</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G157" t="s">
-        <v>11</v>
-      </c>
-      <c r="H157" t="s">
         <v>12</v>
       </c>
     </row>

--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42459CCB-AF1A-406E-8021-DDAE57155CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB44E27-19AC-4E9B-A864-F2454C36CC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="200">
   <si>
     <t>차량명</t>
   </si>
@@ -190,18 +190,12 @@
     <t>쏘나타 디 엣지(DN8)</t>
   </si>
   <si>
-    <t>쏘나타 디 엣지 하이브리드(DN8)</t>
-  </si>
-  <si>
     <t>19~23년</t>
   </si>
   <si>
     <t>쏘나타 (DN8)</t>
   </si>
   <si>
-    <t>쏘나타 하이브리드 (DN8)</t>
-  </si>
-  <si>
     <t>쏘나타 뉴 라이즈</t>
   </si>
   <si>
@@ -448,9 +442,6 @@
     <t>캐스퍼</t>
   </si>
   <si>
-    <t>더 뉴 캐스퍼</t>
-  </si>
-  <si>
     <t>21~24년</t>
   </si>
   <si>
@@ -460,16 +451,7 @@
     <t>코나 (SX2)</t>
   </si>
   <si>
-    <t>코나 하이브리드 (SX2)</t>
-  </si>
-  <si>
-    <t>코나 일렉트릭 (SX2)</t>
-  </si>
-  <si>
     <t>더 뉴 코나</t>
-  </si>
-  <si>
-    <t>더 뉴 코나 하이브리드</t>
   </si>
   <si>
     <t>17~20년</t>
@@ -1142,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1157,7 +1139,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1192,13 +1174,13 @@
         <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -1218,13 +1200,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G3" t="s">
         <v>11</v>
@@ -1244,13 +1226,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -1270,13 +1252,13 @@
         <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -1296,13 +1278,13 @@
         <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1322,16 +1304,16 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
@@ -1348,13 +1330,13 @@
         <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -1374,13 +1356,13 @@
         <v>18</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -1400,16 +1382,16 @@
         <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1423,13 +1405,13 @@
         <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1449,13 +1431,13 @@
         <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -1475,13 +1457,13 @@
         <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1501,13 +1483,13 @@
         <v>22</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1524,16 +1506,16 @@
         <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1553,13 +1535,13 @@
         <v>22</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1579,13 +1561,13 @@
         <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1605,13 +1587,13 @@
         <v>26</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1631,13 +1613,13 @@
         <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -1657,13 +1639,13 @@
         <v>28</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E20" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -1683,13 +1665,13 @@
         <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -1709,16 +1691,16 @@
         <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
         <v>32</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H22" t="s">
         <v>12</v>
@@ -1735,16 +1717,16 @@
         <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H23" t="s">
         <v>12</v>
@@ -1761,16 +1743,16 @@
         <v>33</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1787,16 +1769,16 @@
         <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1813,16 +1795,16 @@
         <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E26" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H26" t="s">
         <v>12</v>
@@ -1839,16 +1821,16 @@
         <v>35</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
         <v>12</v>
@@ -1865,13 +1847,13 @@
         <v>35</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G28" t="s">
         <v>11</v>
@@ -1891,16 +1873,16 @@
         <v>37</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E29" t="s">
         <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -1917,16 +1899,16 @@
         <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H30" t="s">
         <v>12</v>
@@ -1943,13 +1925,13 @@
         <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G31" t="s">
         <v>11</v>
@@ -1969,16 +1951,16 @@
         <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E32" t="s">
         <v>40</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1995,16 +1977,16 @@
         <v>39</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E33" t="s">
         <v>40</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H33" t="s">
         <v>12</v>
@@ -2021,13 +2003,13 @@
         <v>39</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G34" t="s">
         <v>11</v>
@@ -2047,16 +2029,16 @@
         <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
         <v>42</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -2073,16 +2055,16 @@
         <v>43</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E36" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -2099,13 +2081,13 @@
         <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
         <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G37" t="s">
         <v>11</v>
@@ -2125,13 +2107,13 @@
         <v>31</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
         <v>47</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2151,13 +2133,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -2177,13 +2159,13 @@
         <v>33</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -2203,13 +2185,13 @@
         <v>33</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2229,13 +2211,13 @@
         <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2255,16 +2237,16 @@
         <v>35</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E43" t="s">
         <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H43" t="s">
         <v>12</v>
@@ -2281,13 +2263,13 @@
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E44" t="s">
         <v>48</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G44" t="s">
         <v>11</v>
@@ -2307,16 +2289,16 @@
         <v>37</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E45" t="s">
         <v>49</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H45" t="s">
         <v>12</v>
@@ -2333,13 +2315,13 @@
         <v>37</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E46" t="s">
         <v>49</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G46" t="s">
         <v>11</v>
@@ -2359,13 +2341,13 @@
         <v>50</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E47" t="s">
         <v>51</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -2385,13 +2367,13 @@
         <v>50</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E48" t="s">
         <v>51</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2411,13 +2393,13 @@
         <v>52</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E49" t="s">
         <v>53</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G49" t="s">
         <v>11</v>
@@ -2437,13 +2419,13 @@
         <v>52</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G50" t="s">
         <v>11</v>
@@ -2463,13 +2445,13 @@
         <v>52</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E51" t="s">
         <v>53</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G51" t="s">
         <v>11</v>
@@ -2489,13 +2471,13 @@
         <v>31</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E52" t="s">
         <v>55</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2515,13 +2497,13 @@
         <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2538,16 +2520,16 @@
         <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E54" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2564,16 +2546,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="s">
+        <v>56</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="E55" t="s">
-        <v>58</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2590,16 +2572,16 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E56" t="s">
         <v>58</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2616,16 +2598,16 @@
         <v>54</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2645,13 +2627,13 @@
         <v>20</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="G58" t="s">
         <v>11</v>
@@ -2671,13 +2653,13 @@
         <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E59" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G59" t="s">
         <v>11</v>
@@ -2693,14 +2675,14 @@
       <c r="B60" t="s">
         <v>54</v>
       </c>
-      <c r="C60" t="s">
-        <v>20</v>
+      <c r="C60" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>158</v>
@@ -2720,16 +2702,16 @@
         <v>54</v>
       </c>
       <c r="C61" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2745,17 +2727,17 @@
       <c r="B62" t="s">
         <v>54</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>166</v>
+      <c r="C62" t="s">
+        <v>60</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2772,16 +2754,16 @@
         <v>54</v>
       </c>
       <c r="C63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E63" t="s">
+        <v>61</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="E63" t="s">
-        <v>63</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="G63" t="s">
         <v>11</v>
@@ -2801,13 +2783,13 @@
         <v>62</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="E64" t="s">
         <v>63</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2827,13 +2809,13 @@
         <v>62</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="E65" t="s">
         <v>63</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G65" t="s">
         <v>11</v>
@@ -2853,13 +2835,13 @@
         <v>64</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E66" t="s">
         <v>65</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G66" t="s">
         <v>11</v>
@@ -2879,13 +2861,13 @@
         <v>64</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E67" t="s">
         <v>65</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G67" t="s">
         <v>11</v>
@@ -2905,13 +2887,13 @@
         <v>66</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E68" t="s">
         <v>67</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2928,16 +2910,16 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E69" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2957,13 +2939,13 @@
         <v>68</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E70" t="s">
         <v>69</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G70" t="s">
         <v>11</v>
@@ -2980,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E71" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G71" t="s">
         <v>11</v>
@@ -3003,22 +2985,22 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="E72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G72" t="s">
-        <v>11</v>
+        <v>161</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -3029,22 +3011,22 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="E73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G73" t="s">
-        <v>11</v>
+        <v>161</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="H73" t="s">
         <v>12</v>
@@ -3055,22 +3037,22 @@
         <v>7</v>
       </c>
       <c r="B74" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" t="s">
+        <v>71</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" t="s">
         <v>72</v>
       </c>
-      <c r="C74" t="s">
-        <v>73</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E74" t="s">
-        <v>74</v>
-      </c>
       <c r="F74" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H74" t="s">
         <v>12</v>
@@ -3081,22 +3063,22 @@
         <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C75" t="s">
         <v>73</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E75" t="s">
         <v>74</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H75" t="s">
         <v>12</v>
@@ -3107,22 +3089,22 @@
         <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C76" t="s">
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E76" t="s">
         <v>74</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H76" t="s">
         <v>12</v>
@@ -3133,22 +3115,22 @@
         <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C77" t="s">
         <v>75</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E77" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H77" t="s">
         <v>12</v>
@@ -3159,22 +3141,22 @@
         <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C78" t="s">
         <v>75</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E78" t="s">
+        <v>70</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G78" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E78" t="s">
-        <v>76</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -3185,22 +3167,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C79" t="s">
+        <v>31</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E79" t="s">
         <v>77</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E79" t="s">
-        <v>72</v>
-      </c>
       <c r="F79" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3211,22 +3193,22 @@
         <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C80" t="s">
+        <v>31</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E80" t="s">
         <v>77</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E80" t="s">
-        <v>72</v>
-      </c>
       <c r="F80" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -3237,22 +3219,22 @@
         <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
         <v>31</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -3263,19 +3245,19 @@
         <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E82" t="s">
         <v>79</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
@@ -3289,19 +3271,19 @@
         <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G83" t="s">
         <v>11</v>
@@ -3315,19 +3297,19 @@
         <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C84" t="s">
         <v>33</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -3341,19 +3323,19 @@
         <v>7</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C85" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E85" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
@@ -3367,19 +3349,19 @@
         <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C86" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E86" t="s">
         <v>82</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="G86" t="s">
         <v>11</v>
@@ -3393,19 +3375,19 @@
         <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C87" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E87" t="s">
         <v>83</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E87" t="s">
-        <v>84</v>
-      </c>
       <c r="F87" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
@@ -3419,19 +3401,19 @@
         <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C88" t="s">
+        <v>39</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E88" t="s">
         <v>83</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E88" t="s">
-        <v>84</v>
-      </c>
       <c r="F88" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G88" t="s">
         <v>11</v>
@@ -3445,19 +3427,19 @@
         <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G89" t="s">
         <v>11</v>
@@ -3471,19 +3453,19 @@
         <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E90" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G90" t="s">
         <v>11</v>
@@ -3497,22 +3479,22 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E91" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G91" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -3523,19 +3505,19 @@
         <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C92" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E92" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="G92" t="s">
         <v>11</v>
@@ -3549,22 +3531,22 @@
         <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C93" t="s">
         <v>88</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E93" t="s">
         <v>89</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -3575,19 +3557,19 @@
         <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C94" t="s">
         <v>88</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E94" t="s">
         <v>89</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G94" t="s">
         <v>11</v>
@@ -3601,22 +3583,22 @@
         <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C95" t="s">
         <v>90</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E95" t="s">
         <v>91</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="H95" t="s">
         <v>12</v>
@@ -3627,19 +3609,19 @@
         <v>7</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C96" t="s">
         <v>90</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E96" t="s">
         <v>91</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="G96" t="s">
         <v>11</v>
@@ -3653,22 +3635,22 @@
         <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C97" t="s">
         <v>92</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E97" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -3679,19 +3661,19 @@
         <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C98" t="s">
         <v>92</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E98" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3705,19 +3687,19 @@
         <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C99" t="s">
+        <v>93</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E99" t="s">
         <v>94</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E99" t="s">
-        <v>87</v>
-      </c>
       <c r="F99" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
@@ -3731,19 +3713,19 @@
         <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C100" t="s">
+        <v>93</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E100" t="s">
         <v>94</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E100" t="s">
-        <v>87</v>
-      </c>
       <c r="F100" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -3757,19 +3739,19 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C101" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E101" t="s">
-        <v>96</v>
+        <v>154</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="G101" t="s">
         <v>11</v>
@@ -3783,19 +3765,19 @@
         <v>7</v>
       </c>
       <c r="B102" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C102" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E102" t="s">
-        <v>96</v>
+        <v>157</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -3809,19 +3791,19 @@
         <v>7</v>
       </c>
       <c r="B103" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>175</v>
+        <v>162</v>
+      </c>
+      <c r="E103" t="s">
+        <v>95</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
@@ -3835,19 +3817,19 @@
         <v>7</v>
       </c>
       <c r="B104" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C104" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>175</v>
+        <v>157</v>
+      </c>
+      <c r="E104" t="s">
+        <v>95</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="G104" t="s">
         <v>11</v>
@@ -3861,19 +3843,19 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C105" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="E105" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G105" t="s">
         <v>11</v>
@@ -3887,19 +3869,19 @@
         <v>7</v>
       </c>
       <c r="B106" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C106" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E106" t="s">
+        <v>101</v>
+      </c>
+      <c r="F106" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E106" t="s">
-        <v>97</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3913,19 +3895,19 @@
         <v>7</v>
       </c>
       <c r="B107" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E107" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3939,19 +3921,19 @@
         <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C108" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E108" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -3968,19 +3950,19 @@
         <v>102</v>
       </c>
       <c r="C109" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E109" t="s">
         <v>102</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G109" t="s">
-        <v>11</v>
+        <v>172</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="H109" t="s">
         <v>12</v>
@@ -3991,19 +3973,19 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C110" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>176</v>
+        <v>154</v>
       </c>
       <c r="E110" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="G110" t="s">
         <v>11</v>
@@ -4023,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E111" t="s">
         <v>104</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G111" s="1" t="s">
         <v>173</v>
+      </c>
+      <c r="G111" t="s">
+        <v>11</v>
       </c>
       <c r="H111" t="s">
         <v>12</v>
@@ -4049,13 +4031,13 @@
         <v>107</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E112" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4075,13 +4057,13 @@
         <v>107</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E113" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4095,22 +4077,22 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C114" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E114" t="s">
         <v>110</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G114" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H114" t="s">
         <v>12</v>
@@ -4121,22 +4103,22 @@
         <v>7</v>
       </c>
       <c r="B115" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C115" t="s">
+        <v>66</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E115" t="s">
         <v>109</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E115" t="s">
-        <v>110</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="G115" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H115" t="s">
         <v>12</v>
@@ -4150,19 +4132,19 @@
         <v>111</v>
       </c>
       <c r="C116" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
+      </c>
+      <c r="G116" t="s">
+        <v>11</v>
       </c>
       <c r="H116" t="s">
         <v>12</v>
@@ -4176,19 +4158,19 @@
         <v>111</v>
       </c>
       <c r="C117" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E117" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4199,19 +4181,19 @@
         <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C118" t="s">
         <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E118" t="s">
         <v>115</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G118" t="s">
         <v>11</v>
@@ -4225,22 +4207,22 @@
         <v>7</v>
       </c>
       <c r="B119" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C119" t="s">
         <v>114</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="E119" t="s">
         <v>115</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4251,19 +4233,19 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C120" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E120" t="s">
         <v>117</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="G120" t="s">
         <v>11</v>
@@ -4277,22 +4259,22 @@
         <v>7</v>
       </c>
       <c r="B121" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E121" t="s">
         <v>117</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>181</v>
+        <v>151</v>
+      </c>
+      <c r="G121" t="s">
+        <v>11</v>
       </c>
       <c r="H121" t="s">
         <v>12</v>
@@ -4303,19 +4285,19 @@
         <v>7</v>
       </c>
       <c r="B122" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C122" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E122" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G122" t="s">
         <v>11</v>
@@ -4329,19 +4311,19 @@
         <v>7</v>
       </c>
       <c r="B123" t="s">
+        <v>116</v>
+      </c>
+      <c r="C123" t="s">
         <v>118</v>
       </c>
-      <c r="C123" t="s">
-        <v>73</v>
-      </c>
       <c r="D123" s="1" t="s">
-        <v>162</v>
+        <v>191</v>
       </c>
       <c r="E123" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G123" t="s">
         <v>11</v>
@@ -4355,19 +4337,19 @@
         <v>7</v>
       </c>
       <c r="B124" t="s">
+        <v>116</v>
+      </c>
+      <c r="C124" t="s">
         <v>118</v>
       </c>
-      <c r="C124" t="s">
-        <v>73</v>
-      </c>
       <c r="D124" s="1" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E124" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G124" t="s">
         <v>11</v>
@@ -4381,19 +4363,19 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
+        <v>116</v>
+      </c>
+      <c r="C125" t="s">
         <v>118</v>
       </c>
-      <c r="C125" t="s">
-        <v>120</v>
-      </c>
       <c r="D125" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E125" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G125" t="s">
         <v>11</v>
@@ -4407,19 +4389,19 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C126" t="s">
         <v>120</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E126" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -4433,19 +4415,19 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C127" t="s">
-        <v>120</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>199</v>
+        <v>97</v>
+      </c>
+      <c r="D127" t="s">
+        <v>98</v>
       </c>
       <c r="E127" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
@@ -4462,16 +4444,16 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>122</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>198</v>
+        <v>123</v>
+      </c>
+      <c r="D128" t="s">
+        <v>98</v>
       </c>
       <c r="E128" t="s">
         <v>121</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G128" t="s">
         <v>11</v>
@@ -4485,19 +4467,19 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C129" t="s">
-        <v>99</v>
-      </c>
-      <c r="D129" t="s">
-        <v>100</v>
+        <v>71</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="E129" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G129" t="s">
         <v>11</v>
@@ -4511,19 +4493,19 @@
         <v>7</v>
       </c>
       <c r="B130" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C130" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="D130" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E130" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G130" t="s">
         <v>11</v>
@@ -4540,16 +4522,16 @@
         <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E131" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G131" t="s">
         <v>11</v>
@@ -4563,19 +4545,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C132" t="s">
-        <v>75</v>
-      </c>
-      <c r="D132" t="s">
-        <v>100</v>
+        <v>128</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="E132" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4589,22 +4571,22 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C133" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="E133" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G133" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H133" t="s">
         <v>12</v>
@@ -4615,22 +4597,22 @@
         <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C134" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E134" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G134" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H134" t="s">
         <v>12</v>
@@ -4641,22 +4623,22 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C135" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E135" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>165</v>
+        <v>178</v>
+      </c>
+      <c r="G135" t="s">
+        <v>11</v>
       </c>
       <c r="H135" t="s">
         <v>12</v>
@@ -4667,22 +4649,22 @@
         <v>7</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C136" t="s">
+        <v>136</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E136" t="s">
         <v>133</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E136" t="s">
-        <v>134</v>
-      </c>
       <c r="F136" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+      <c r="G136" t="s">
+        <v>11</v>
       </c>
       <c r="H136" t="s">
         <v>12</v>
@@ -4693,19 +4675,19 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C137" t="s">
-        <v>136</v>
+        <v>22</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E137" t="s">
         <v>137</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4719,19 +4701,19 @@
         <v>7</v>
       </c>
       <c r="B138" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C138" t="s">
+        <v>93</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E138" t="s">
         <v>138</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E138" t="s">
-        <v>135</v>
-      </c>
       <c r="F138" s="1" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="G138" t="s">
         <v>11</v>
@@ -4745,19 +4727,19 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C139" t="s">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="E139" t="s">
         <v>139</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G139" t="s">
         <v>11</v>
@@ -4771,19 +4753,19 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C140" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="E140" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G140" t="s">
         <v>11</v>
@@ -4800,19 +4782,19 @@
         <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G141" t="s">
-        <v>11</v>
+        <v>165</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H141" t="s">
         <v>12</v>
@@ -4826,19 +4808,19 @@
         <v>141</v>
       </c>
       <c r="C142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="E142" t="s">
         <v>141</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G142" t="s">
-        <v>11</v>
+        <v>165</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H142" t="s">
         <v>12</v>
@@ -4849,22 +4831,22 @@
         <v>7</v>
       </c>
       <c r="B143" t="s">
+        <v>141</v>
+      </c>
+      <c r="C143" t="s">
         <v>144</v>
       </c>
-      <c r="C143" t="s">
-        <v>31</v>
-      </c>
       <c r="D143" s="1" t="s">
-        <v>198</v>
+        <v>157</v>
       </c>
       <c r="E143" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="G143" t="s">
-        <v>11</v>
+        <v>165</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H143" t="s">
         <v>12</v>
@@ -4875,19 +4857,19 @@
         <v>7</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="E144" t="s">
         <v>146</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="G144" t="s">
         <v>11</v>
@@ -4901,19 +4883,19 @@
         <v>7</v>
       </c>
       <c r="B145" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="D145" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E145" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="G145" t="s">
         <v>11</v>
@@ -4927,22 +4909,22 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C146" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="E146" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
+      </c>
+      <c r="G146" t="s">
+        <v>11</v>
       </c>
       <c r="H146" t="s">
         <v>12</v>
@@ -4953,180 +4935,24 @@
         <v>7</v>
       </c>
       <c r="B147" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C147" t="s">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="E147" t="s">
         <v>149</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G147" t="s">
         <v>11</v>
       </c>
       <c r="H147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" t="s">
-        <v>7</v>
-      </c>
-      <c r="B148" t="s">
-        <v>144</v>
-      </c>
-      <c r="C148" t="s">
-        <v>150</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E148" t="s">
-        <v>144</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G148" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H148" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" t="s">
-        <v>7</v>
-      </c>
-      <c r="B149" t="s">
-        <v>144</v>
-      </c>
-      <c r="C149" t="s">
-        <v>150</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E149" t="s">
-        <v>144</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H149" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" t="s">
-        <v>7</v>
-      </c>
-      <c r="B150" t="s">
-        <v>144</v>
-      </c>
-      <c r="C150" t="s">
-        <v>151</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E150" t="s">
-        <v>152</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G150" t="s">
-        <v>11</v>
-      </c>
-      <c r="H150" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
-      <c r="A151" t="s">
-        <v>7</v>
-      </c>
-      <c r="B151" t="s">
-        <v>144</v>
-      </c>
-      <c r="C151" t="s">
-        <v>153</v>
-      </c>
-      <c r="D151" t="s">
-        <v>100</v>
-      </c>
-      <c r="E151" t="s">
-        <v>154</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G151" t="s">
-        <v>11</v>
-      </c>
-      <c r="H151" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
-      <c r="A152" t="s">
-        <v>7</v>
-      </c>
-      <c r="B152" t="s">
-        <v>155</v>
-      </c>
-      <c r="C152" t="s">
-        <v>101</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E152" t="s">
-        <v>155</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G152" t="s">
-        <v>11</v>
-      </c>
-      <c r="H152" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153" t="s">
-        <v>7</v>
-      </c>
-      <c r="B153" t="s">
-        <v>155</v>
-      </c>
-      <c r="C153" t="s">
-        <v>101</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E153" t="s">
-        <v>155</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G153" t="s">
-        <v>11</v>
-      </c>
-      <c r="H153" t="s">
         <v>12</v>
       </c>
     </row>

--- a/master-db/hyundai.xlsx
+++ b/master-db/hyundai.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kang1\Documents\GitHub\ildeung-battery-v1\master-db\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB44E27-19AC-4E9B-A864-F2454C36CC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7694C33-6DBA-4FFF-A60B-E866ABAEBA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="208">
   <si>
     <t>차량명</t>
   </si>
@@ -679,38 +679,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AGM70</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>대기</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>가솔린 2.5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>가솔린 3.3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">그랜저 IG </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>그랜저 IG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -762,6 +739,83 @@
   </si>
   <si>
     <t>더 뉴 싼타페 하이브리드 TM</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜저</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>9~22년</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>가솔린 2.5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>더 뉴 그랜저 IG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AGM70</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2~26년</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>그랜저 (GN7)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>더 뉴 스타리아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> 하이브리드</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타리아 하이브리드</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1124,7 +1178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1242,29 +1296,26 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
+      <c r="A5" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
+        <v>200</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
+        <v>202</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1275,16 +1326,16 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -1304,45 +1355,42 @@
         <v>15</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
       </c>
       <c r="H7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
+      <c r="A8" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
+        <v>200</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
+        <v>202</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1353,20 +1401,18 @@
         <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" t="s">
-        <v>11</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G9" s="1"/>
       <c r="H9" t="s">
         <v>12</v>
       </c>
@@ -1379,19 +1425,22 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>188</v>
+        <v>156</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>185</v>
+        <v>158</v>
+      </c>
+      <c r="G10" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1405,13 +1454,13 @@
         <v>18</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>189</v>
+        <v>155</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -1431,19 +1480,16 @@
         <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
+        <v>154</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G12" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" t="s">
-        <v>12</v>
+      <c r="H12" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1454,16 +1500,16 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -1480,16 +1526,16 @@
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -1505,17 +1551,17 @@
       <c r="B15" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>181</v>
+      <c r="C15" t="s">
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -1531,17 +1577,17 @@
       <c r="B16" t="s">
         <v>8</v>
       </c>
-      <c r="C16" t="s">
-        <v>22</v>
+      <c r="C16" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1558,16 +1604,16 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -1584,16 +1630,16 @@
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -1613,7 +1659,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -1636,13 +1682,13 @@
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>153</v>
@@ -1665,7 +1711,7 @@
         <v>28</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21" t="s">
         <v>29</v>
@@ -1685,22 +1731,22 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
+      </c>
+      <c r="G22" t="s">
+        <v>11</v>
       </c>
       <c r="H22" t="s">
         <v>12</v>
@@ -1717,7 +1763,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
@@ -1740,19 +1786,19 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H24" t="s">
         <v>12</v>
@@ -1769,16 +1815,16 @@
         <v>33</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
         <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H25" t="s">
         <v>12</v>
@@ -1792,19 +1838,19 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H26" t="s">
         <v>12</v>
@@ -1821,7 +1867,7 @@
         <v>35</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E27" t="s">
         <v>36</v>
@@ -1847,16 +1893,16 @@
         <v>35</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H28" t="s">
         <v>12</v>
@@ -1870,19 +1916,19 @@
         <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
       </c>
       <c r="H29" t="s">
         <v>12</v>
@@ -1899,7 +1945,7 @@
         <v>37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
         <v>38</v>
@@ -1925,16 +1971,16 @@
         <v>37</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G31" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H31" t="s">
         <v>12</v>
@@ -1948,19 +1994,19 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
       </c>
       <c r="H32" t="s">
         <v>12</v>
@@ -1977,7 +2023,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="E33" t="s">
         <v>40</v>
@@ -2003,16 +2049,16 @@
         <v>39</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G34" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H34" t="s">
         <v>12</v>
@@ -2026,19 +2072,19 @@
         <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
       </c>
       <c r="H35" t="s">
         <v>12</v>
@@ -2052,19 +2098,19 @@
         <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H36" t="s">
         <v>12</v>
@@ -2081,16 +2127,16 @@
         <v>43</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E37" t="s">
         <v>44</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
       </c>
       <c r="H37" t="s">
         <v>12</v>
@@ -2101,19 +2147,19 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G38" t="s">
         <v>11</v>
@@ -2133,13 +2179,13 @@
         <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>198</v>
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G39" t="s">
         <v>11</v>
@@ -2156,16 +2202,16 @@
         <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G40" t="s">
         <v>11</v>
@@ -2185,13 +2231,13 @@
         <v>33</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="G41" t="s">
         <v>11</v>
@@ -2211,13 +2257,13 @@
         <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="G42" t="s">
         <v>11</v>
@@ -2234,19 +2280,19 @@
         <v>46</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E43" t="s">
-        <v>48</v>
+        <v>157</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>163</v>
+      <c r="G43" t="s">
+        <v>11</v>
       </c>
       <c r="H43" t="s">
         <v>12</v>
@@ -2263,16 +2309,16 @@
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E44" t="s">
         <v>48</v>
       </c>
       <c r="F44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="G44" t="s">
-        <v>11</v>
       </c>
       <c r="H44" t="s">
         <v>12</v>
@@ -2286,19 +2332,19 @@
         <v>46</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G45" s="1" t="s">
         <v>163</v>
+      </c>
+      <c r="G45" t="s">
+        <v>11</v>
       </c>
       <c r="H45" t="s">
         <v>12</v>
@@ -2315,16 +2361,16 @@
         <v>37</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E46" t="s">
         <v>49</v>
       </c>
       <c r="F46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="G46" t="s">
-        <v>11</v>
       </c>
       <c r="H46" t="s">
         <v>12</v>
@@ -2338,16 +2384,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G47" t="s">
         <v>11</v>
@@ -2367,13 +2413,13 @@
         <v>50</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E48" t="s">
         <v>51</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G48" t="s">
         <v>11</v>
@@ -2390,13 +2436,13 @@
         <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>171</v>
@@ -2419,7 +2465,7 @@
         <v>52</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="E50" t="s">
         <v>53</v>
@@ -2445,7 +2491,7 @@
         <v>52</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E51" t="s">
         <v>53</v>
@@ -2465,19 +2511,19 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="G52" t="s">
         <v>11</v>
@@ -2497,13 +2543,13 @@
         <v>31</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G53" t="s">
         <v>11</v>
@@ -2520,16 +2566,16 @@
         <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G54" t="s">
         <v>11</v>
@@ -2549,13 +2595,13 @@
         <v>56</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
         <v>57</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G55" t="s">
         <v>11</v>
@@ -2572,16 +2618,16 @@
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G56" t="s">
         <v>11</v>
@@ -2601,13 +2647,13 @@
         <v>20</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E57" t="s">
         <v>58</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G57" t="s">
         <v>11</v>
@@ -2653,7 +2699,7 @@
         <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E59" t="s">
         <v>58</v>
@@ -2675,17 +2721,17 @@
       <c r="B60" t="s">
         <v>54</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>160</v>
+      <c r="C60" t="s">
+        <v>20</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="G60" t="s">
         <v>11</v>
@@ -2701,17 +2747,17 @@
       <c r="B61" t="s">
         <v>54</v>
       </c>
-      <c r="C61" t="s">
-        <v>60</v>
+      <c r="C61" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E61" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G61" t="s">
         <v>11</v>
@@ -2731,13 +2777,13 @@
         <v>60</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="G62" t="s">
         <v>11</v>
@@ -2757,7 +2803,7 @@
         <v>60</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
@@ -2780,16 +2826,16 @@
         <v>54</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="E64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="G64" t="s">
         <v>11</v>
@@ -2809,7 +2855,7 @@
         <v>62</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E65" t="s">
         <v>63</v>
@@ -2832,13 +2878,13 @@
         <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>153</v>
@@ -2861,7 +2907,7 @@
         <v>64</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E67" t="s">
         <v>65</v>
@@ -2884,16 +2930,16 @@
         <v>54</v>
       </c>
       <c r="C68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G68" t="s">
         <v>11</v>
@@ -2910,16 +2956,16 @@
         <v>54</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E69" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G69" t="s">
         <v>11</v>
@@ -2939,7 +2985,7 @@
         <v>68</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E70" t="s">
         <v>69</v>
@@ -2965,7 +3011,7 @@
         <v>68</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E71" t="s">
         <v>69</v>
@@ -2985,22 +3031,22 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="E72" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -3017,7 +3063,7 @@
         <v>71</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E73" t="s">
         <v>72</v>
@@ -3066,13 +3112,13 @@
         <v>70</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E75" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>161</v>
@@ -3095,7 +3141,7 @@
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E76" t="s">
         <v>74</v>
@@ -3118,13 +3164,13 @@
         <v>70</v>
       </c>
       <c r="C77" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E77" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>161</v>
@@ -3147,7 +3193,7 @@
         <v>75</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E78" t="s">
         <v>70</v>
@@ -3167,22 +3213,22 @@
         <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E79" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -3199,16 +3245,16 @@
         <v>31</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E80" t="s">
         <v>77</v>
       </c>
       <c r="F80" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G80" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="G80" t="s">
-        <v>11</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -3225,13 +3271,13 @@
         <v>31</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E81" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G81" t="s">
         <v>11</v>
@@ -3248,16 +3294,16 @@
         <v>76</v>
       </c>
       <c r="C82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E82" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G82" t="s">
         <v>11</v>
@@ -3277,13 +3323,13 @@
         <v>33</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E83" t="s">
         <v>79</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G83" t="s">
         <v>11</v>
@@ -3303,13 +3349,13 @@
         <v>33</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G84" t="s">
         <v>11</v>
@@ -3326,16 +3372,16 @@
         <v>76</v>
       </c>
       <c r="C85" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E85" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G85" t="s">
         <v>11</v>
@@ -3355,7 +3401,7 @@
         <v>81</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E86" t="s">
         <v>82</v>
@@ -3378,16 +3424,16 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E87" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G87" t="s">
         <v>11</v>
@@ -3407,7 +3453,7 @@
         <v>39</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E88" t="s">
         <v>83</v>
@@ -3430,13 +3476,13 @@
         <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>166</v>
@@ -3459,7 +3505,7 @@
         <v>45</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E90" t="s">
         <v>84</v>
@@ -3479,22 +3525,22 @@
         <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C91" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E91" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>159</v>
+        <v>166</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -3511,16 +3557,16 @@
         <v>86</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E92" t="s">
         <v>87</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G92" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="H92" t="s">
         <v>12</v>
@@ -3534,19 +3580,19 @@
         <v>85</v>
       </c>
       <c r="C93" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -3563,16 +3609,16 @@
         <v>88</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E94" t="s">
         <v>89</v>
       </c>
       <c r="F94" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G94" t="s">
-        <v>11</v>
       </c>
       <c r="H94" t="s">
         <v>12</v>
@@ -3586,19 +3632,19 @@
         <v>85</v>
       </c>
       <c r="C95" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E95" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G95" s="1" t="s">
         <v>159</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
       </c>
       <c r="H95" t="s">
         <v>12</v>
@@ -3615,16 +3661,16 @@
         <v>90</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E96" t="s">
         <v>91</v>
       </c>
       <c r="F96" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G96" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G96" t="s">
-        <v>11</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -3638,16 +3684,16 @@
         <v>85</v>
       </c>
       <c r="C97" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G97" t="s">
         <v>11</v>
@@ -3667,13 +3713,13 @@
         <v>92</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E98" t="s">
         <v>85</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G98" t="s">
         <v>11</v>
@@ -3690,16 +3736,16 @@
         <v>85</v>
       </c>
       <c r="C99" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E99" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="G99" t="s">
         <v>11</v>
@@ -3719,13 +3765,13 @@
         <v>93</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E100" t="s">
         <v>94</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G100" t="s">
         <v>11</v>
@@ -3739,16 +3785,16 @@
         <v>7</v>
       </c>
       <c r="B101" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C101" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
+      </c>
+      <c r="E101" t="s">
+        <v>94</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>153</v>
@@ -3771,13 +3817,13 @@
         <v>96</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>169</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="G102" t="s">
         <v>11</v>
@@ -3794,16 +3840,16 @@
         <v>95</v>
       </c>
       <c r="C103" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E103" t="s">
-        <v>95</v>
+        <v>157</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="G103" t="s">
         <v>11</v>
@@ -3823,7 +3869,7 @@
         <v>90</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E104" t="s">
         <v>95</v>
@@ -3843,16 +3889,16 @@
         <v>7</v>
       </c>
       <c r="B105" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C105" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>153</v>
@@ -3875,13 +3921,13 @@
         <v>96</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E106" t="s">
         <v>101</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G106" t="s">
         <v>11</v>
@@ -3898,16 +3944,16 @@
         <v>100</v>
       </c>
       <c r="C107" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E107" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G107" t="s">
         <v>11</v>
@@ -3927,13 +3973,13 @@
         <v>39</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E108" t="s">
         <v>100</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="G108" t="s">
         <v>11</v>
@@ -3947,22 +3993,22 @@
         <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C109" t="s">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E109" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="G109" t="s">
+        <v>11</v>
       </c>
       <c r="H109" t="s">
         <v>12</v>
@@ -3973,22 +4019,22 @@
         <v>7</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C110" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E110" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="G110" t="s">
-        <v>11</v>
+        <v>172</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="H110" t="s">
         <v>12</v>
@@ -4005,13 +4051,13 @@
         <v>105</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E111" t="s">
         <v>104</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="G111" t="s">
         <v>11</v>
@@ -4025,19 +4071,19 @@
         <v>7</v>
       </c>
       <c r="B112" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E112" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="G112" t="s">
         <v>11</v>
@@ -4057,13 +4103,13 @@
         <v>107</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E113" t="s">
         <v>108</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G113" t="s">
         <v>11</v>
@@ -4077,22 +4123,22 @@
         <v>7</v>
       </c>
       <c r="B114" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C114" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E114" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>164</v>
+        <v>153</v>
+      </c>
+      <c r="G114" t="s">
+        <v>11</v>
       </c>
       <c r="H114" t="s">
         <v>12</v>
@@ -4106,13 +4152,13 @@
         <v>109</v>
       </c>
       <c r="C115" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E115" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>167</v>
@@ -4129,22 +4175,22 @@
         <v>7</v>
       </c>
       <c r="B116" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C116" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E116" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G116" t="s">
-        <v>11</v>
+        <v>167</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H116" t="s">
         <v>12</v>
@@ -4161,16 +4207,16 @@
         <v>112</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E117" t="s">
         <v>113</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="G117" t="s">
+        <v>11</v>
       </c>
       <c r="H117" t="s">
         <v>12</v>
@@ -4184,19 +4230,19 @@
         <v>111</v>
       </c>
       <c r="C118" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E118" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="G118" t="s">
-        <v>11</v>
+        <v>166</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H118" t="s">
         <v>12</v>
@@ -4213,16 +4259,16 @@
         <v>114</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E119" t="s">
         <v>115</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="G119" t="s">
+        <v>11</v>
       </c>
       <c r="H119" t="s">
         <v>12</v>
@@ -4233,22 +4279,22 @@
         <v>7</v>
       </c>
       <c r="B120" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C120" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E120" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G120" t="s">
-        <v>11</v>
+        <v>166</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="H120" t="s">
         <v>12</v>
@@ -4265,7 +4311,7 @@
         <v>71</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E121" t="s">
         <v>117</v>
@@ -4291,10 +4337,10 @@
         <v>71</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E122" t="s">
-        <v>117</v>
+        <v>156</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>151</v>
@@ -4314,13 +4360,13 @@
         <v>116</v>
       </c>
       <c r="C123" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="E123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>151</v>
@@ -4343,7 +4389,7 @@
         <v>118</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E124" t="s">
         <v>116</v>
@@ -4369,10 +4415,10 @@
         <v>118</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E125" t="s">
-        <v>116</v>
+        <v>191</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>151</v>
@@ -4389,19 +4435,19 @@
         <v>7</v>
       </c>
       <c r="B126" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C126" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E126" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G126" t="s">
         <v>11</v>
@@ -4415,19 +4461,19 @@
         <v>7</v>
       </c>
       <c r="B127" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C127" t="s">
-        <v>97</v>
-      </c>
-      <c r="D127" t="s">
-        <v>98</v>
+        <v>120</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="E127" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="G127" t="s">
         <v>11</v>
@@ -4444,13 +4490,13 @@
         <v>121</v>
       </c>
       <c r="C128" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D128" t="s">
         <v>98</v>
       </c>
       <c r="E128" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>165</v>
@@ -4467,16 +4513,16 @@
         <v>7</v>
       </c>
       <c r="B129" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C129" t="s">
-        <v>71</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>176</v>
+        <v>123</v>
+      </c>
+      <c r="D129" t="s">
+        <v>98</v>
       </c>
       <c r="E129" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>165</v>
@@ -4496,13 +4542,13 @@
         <v>124</v>
       </c>
       <c r="C130" t="s">
-        <v>73</v>
-      </c>
-      <c r="D130" t="s">
-        <v>98</v>
+        <v>71</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="E130" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>165</v>
@@ -4519,16 +4565,16 @@
         <v>7</v>
       </c>
       <c r="B131" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C131" t="s">
-        <v>71</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>176</v>
+        <v>73</v>
+      </c>
+      <c r="D131" t="s">
+        <v>98</v>
       </c>
       <c r="E131" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>165</v>
@@ -4545,19 +4591,19 @@
         <v>7</v>
       </c>
       <c r="B132" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="E132" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="G132" t="s">
         <v>11</v>
@@ -4571,22 +4617,22 @@
         <v>7</v>
       </c>
       <c r="B133" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C133" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E133" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>159</v>
+        <v>177</v>
+      </c>
+      <c r="G133" t="s">
+        <v>11</v>
       </c>
       <c r="H133" t="s">
         <v>12</v>
@@ -4603,16 +4649,16 @@
         <v>131</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E134" t="s">
         <v>132</v>
       </c>
       <c r="F134" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G134" s="1" t="s">
         <v>159</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="H134" t="s">
         <v>12</v>
@@ -4623,22 +4669,22 @@
         <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C135" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E135" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G135" t="s">
-        <v>11</v>
+        <v>159</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H135" t="s">
         <v>12</v>
@@ -4652,16 +4698,16 @@
         <v>133</v>
       </c>
       <c r="C136" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E136" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G136" t="s">
         <v>11</v>
@@ -4678,16 +4724,16 @@
         <v>133</v>
       </c>
       <c r="C137" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E137" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="G137" t="s">
         <v>11</v>
@@ -4704,13 +4750,13 @@
         <v>133</v>
       </c>
       <c r="C138" t="s">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>153</v>
@@ -4727,19 +4773,19 @@
         <v>7</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C139" t="s">
-        <v>140</v>
+        <v>93</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="E139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="G139" t="s">
         <v>11</v>
@@ -4753,19 +4799,19 @@
         <v>7</v>
       </c>
       <c r="B140" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E140" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G140" t="s">
         <v>11</v>
@@ -4782,19 +4828,19 @@
         <v>141</v>
       </c>
       <c r="C141" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="E141" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
+      </c>
+      <c r="G141" t="s">
+        <v>11</v>
       </c>
       <c r="H141" t="s">
         <v>12</v>
@@ -4808,13 +4854,13 @@
         <v>141</v>
       </c>
       <c r="C142" t="s">
-        <v>144</v>
+        <v>33</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>154</v>
       </c>
       <c r="E142" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>165</v>
@@ -4837,7 +4883,7 @@
         <v>144</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E143" t="s">
         <v>141</v>
@@ -4860,19 +4906,19 @@
         <v>141</v>
       </c>
       <c r="C144" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E144" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G144" t="s">
-        <v>11</v>
+        <v>165</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="H144" t="s">
         <v>12</v>
@@ -4886,13 +4932,13 @@
         <v>141</v>
       </c>
       <c r="C145" t="s">
-        <v>147</v>
-      </c>
-      <c r="D145" t="s">
-        <v>98</v>
+        <v>145</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="E145" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>172</v>
@@ -4909,19 +4955,19 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C146" t="s">
-        <v>99</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>195</v>
+        <v>147</v>
+      </c>
+      <c r="D146" t="s">
+        <v>98</v>
       </c>
       <c r="E146" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G146" t="s">
         <v>11</v>
@@ -4941,7 +4987,7 @@
         <v>99</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E147" t="s">
         <v>149</v>
@@ -4953,6 +4999,32 @@
         <v>11</v>
       </c>
       <c r="H147" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>149</v>
+      </c>
+      <c r="C148" t="s">
+        <v>99</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E148" t="s">
+        <v>149</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G148" t="s">
+        <v>11</v>
+      </c>
+      <c r="H148" t="s">
         <v>12</v>
       </c>
     </row>
